--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y203"/>
+  <dimension ref="A1:Y164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,19 +617,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]of</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]of</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): he1 (letter/digit mix) :: ULY 0 â€¢ Office and residence. No. 15 Main he1</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): he1 (letter/digit mix) :: ULY 0 • Office and residence. No. 15 Main he1</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BERLIN, June 8.â€”Wiesinger, who attempt-</t>
+          <t>L375: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | suspicious token(s): dearSirt (odd internal casing) :: GRIP(interrupting）Excellent, my dearSirt</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: J" WEEKLY TIMES,â€� to whom ac-</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -803,24 +807,24 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L240: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BERLIN, June 8.â€” A grand banquet is to be</t>
+          <t>L429: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ETHOMAS, Dentist,â€�-</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): he1 (letter/digit mix) :: ULY 0 • Office and residence. No. 15 Main he1</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L373: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -866,12 +870,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -894,19 +898,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L445: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: DRESS MATERIALS！!</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: :io, FFICE :â€”10 KING ST.,I</t>
+          <t>L802: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •THOMA</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L374: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -916,7 +920,7 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>L1326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wheatâ€”Deihl...</t>
+          <t>L1326: punctuation artifact: repeated periods :: Wheat—Deihl...</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -985,12 +989,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L499: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: Spring Importations of Dry Goods ！</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): he1 (letter/digit mix) :: ULY 0 â€¢ Office and residence. No. 15 Main he1</t>
+          <t>L812: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Starling * at Port Dalhousie</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1076,12 +1080,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hat do you want, young man,â€”soft or stiff?"?"</t>
+          <t>L598: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS :: MR. M. C. C.(Interrupting ） You misun</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Church, "st nearly opposite the â€œdamiyâ€� #</t>
+          <t>L1275: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L102: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1109,7 +1113,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L1271: line starts with punctuation glued to text :: _____17-d&amp;w ______Toronto</t>
+          <t>L802: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •THOMA</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1163,19 +1167,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L392: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAn</t>
+          <t>L851: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: P. MOVED to his residence, Wellingtonâ€� But</t>
+          <t>L1640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -----• ----</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L461: isolated marker/symbol line :: Y</t>
+          <t>L429: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1196,7 +1200,7 @@
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L1296: line starts with punctuation glued to text :: .the trust funds to $5,5000,000 and credited</t>
+          <t>L812: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Starling * at Port Dalhousie</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1250,19 +1254,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L445: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: DRESS MATERIALSï¼�!</t>
+          <t>L936: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: $11,960,700；assets,$38,339,140.21.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Street, Hamiltonâ€”for one day onlyâ€”on the last</t>
+          <t>L1764: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • DR</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L496: isolated marker/symbol line :: H</t>
+          <t>L461: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1283,7 +1287,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L1389: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: .THE BISHOP OF NIAGARA.â€”On Thursday the</t>
+          <t>L1271: line starts with punctuation glued to text :: _____17-d&amp;w ______Toronto</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1309,12 +1313,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1337,19 +1341,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GENAPPINE CLOTH-for Mourningâ€”32 and 35 cents.</t>
+          <t>L1072: stray/suspicious non-ASCII glyph(s): U+914D CJK UNIFIED IDEOGRAPH-914D :: T 配</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1000 AGENTS WANTED,â€”</t>
+          <t>L1857: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • which we desire to send free by mail to every one.</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L504: isolated marker/symbol line :: t</t>
+          <t>L496: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1370,7 +1374,7 @@
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L1580: line starts with punctuation glued to text :: ___ 30th of May, from the premises of James</t>
+          <t>L1296: line starts with punctuation glued to text :: .the trust funds to $5,5000,000 and credited</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1401,7 +1405,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1424,19 +1428,19 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pet Yarns cheap.- Millinery and Mantles made to order.- German Spoken.- ken.â€”Termsâ€”POSITIVELY</t>
+          <t>L1073: stray/suspicious non-ASCII glyph(s): U+914D CJK UNIFIED IDEOGRAPH-914D | isolated marker/symbol line :: 配</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gripâ€”Of course, capitally ! youâ€™ll find him</t>
+          <t>L2000: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to 00</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L510: isolated marker/symbol line :: 0</t>
+          <t>L504: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1451,13 +1455,13 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: , Wheatâ€”Deihl........</t>
+          <t>L1605: punctuation artifact: repeated periods :: , Wheat—Deihl........</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L1640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----â€¢ ----</t>
+          <t>L1389: line starts with punctuation glued to text :: .THE BISHOP OF NIAGARA.—On Thursday the</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1483,12 +1487,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1501,7 +1505,7 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>L375: suspicious token(s): dearSirt (odd internal casing) :: GRIP(interruptingï¼‰Excellent, my dearSirt</t>
+          <t>L375: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | suspicious token(s): dearSirt (odd internal casing) :: GRIP(interrupting）Excellent, my dearSirt</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
@@ -1511,19 +1515,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: Spring Importations of Dry Goods ï¼�</t>
+          <t>L1272: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: It Never Fails！！</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: about MACKELLARâ€™S " fall ploughing." Why,</t>
+          <t>L2341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •chants' Despatch Transportation Çompany</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: J.</t>
+          <t>L510: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1544,7 +1548,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L1838: line starts with digit/letter garbage token | suspicious token(s): 3Cures (letter/digit mix) | candidate OCR token mismatch vs other OCR: "Cures" vs "3Cures" :: 3Cures all Nervous Diseases, such as</t>
+          <t>L1580: line starts with punctuation glued to text :: ___ 30th of May, from the premises of James</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1594,19 +1598,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L501: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: "WEEKLY TIMES,â€�tO whom</t>
+          <t>L1305: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | suspicious token(s): sYRUP (odd internal casing) :: VIAN sYRUP (not Peruvian Bark ） Sold by</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”â€œ Commissioner of Crown</t>
+          <t>L2575: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •9</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: E.</t>
+          <t>L516: isolated marker/symbol line :: J.</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1627,7 +1631,7 @@
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L1863: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 5WILLIAM (letter/digit mix) :: 5WILLIAM GRAY &amp; Co.,...</t>
+          <t>L1764: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • DR</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1654,7 +1658,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1677,19 +1681,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: derstand me, I'm afraid â€” I merely put MR.</t>
+          <t>L1629: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Landsâ€”Mr. Blankâ€”"</t>
+          <t>L2735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L532: isolated marker/symbol line :: D</t>
+          <t>L520: isolated marker/symbol line :: E.</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1710,7 +1714,7 @@
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1877: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _____â€” TER of ALEXAN-</t>
+          <t>L1838: line starts with digit/letter garbage token | suspicious token(s): 3Cures (letter/digit mix) | candidate OCR token mismatch vs other OCR: "Cures" vs "3Cures" :: 3Cures all Nervous Diseases, such as</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1756,19 +1760,19 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: track, which is the " nearest eutâ€� from St.</t>
+          <t>L1630: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: thatâ€™s the best of the lot. If the others were</t>
+          <t>L2763: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L537: isolated marker/symbol line :: 0</t>
+          <t>L532: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1789,7 +1793,7 @@
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>L2686: line starts with punctuation glued to text :: * on the dollar, which is a guarantee that he</t>
+          <t>L1857: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • which we desire to send free by mail to every one.</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr"/>
@@ -1835,24 +1839,20 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: COURT HOUSE CARE TAKER.â€” We learn that</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. M. C. C.â€”(Interrupting) You misun-</t>
-        </is>
-      </c>
+          <t>L1835: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L538: isolated marker/symbol line :: P</t>
+          <t>L537: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L897: isolated marker/symbol line :: Â»</t>
+          <t>L897: isolated marker/symbol line :: »</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1866,7 +1866,11 @@
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L1863: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 5WILLIAM (letter/digit mix) :: 5WILLIAM GRAY &amp; Co.,...</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr">
@@ -1910,19 +1914,15 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TE Crops.â€” Owing: to the long continued</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: derstand me. Iâ€™m afraidâ€”I merely put Mn.</t>
-        </is>
-      </c>
+          <t>L2039: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: situde ，</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L550: symbol-only separator/garbage line :: 1000</t>
+          <t>L538: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1941,7 +1941,11 @@
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L1877: line starts with punctuation glued to text :: _____— TER of ALEXAN-</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr">
@@ -1973,19 +1977,15 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”(Hesitatingly)â€” Ab, th-a-n-ks</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Gripâ€”Wherein it resembles my crop at</t>
-        </is>
-      </c>
+          <t>L2041: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA, U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 :: the Back ， Di 心 sof</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L554: isolated marker/symbol line :: 4</t>
+          <t>L550: symbol-only separator/garbage line :: 1000</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -2004,12 +2004,16 @@
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L2000: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to 00</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr">
         <is>
-          <t>L1748: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr.M.C.C.â€”(Impassionately)â€”Well</t>
+          <t>L1748: abbreviation/spacing may be garbled :: Mr.M.C.C.—(Impassionately)—Well</t>
         </is>
       </c>
       <c r="W18" s="1" t="inlineStr"/>
@@ -2031,24 +2035,20 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1y (letter/digit mix) :: â€”71-1y 95 King St. West.</t>
+          <t>L758: suspicious token(s): 1y (letter/digit mix) :: —71-1y 95 King St. West.</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L1072: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: T é…�</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: this moment, for I havnâ€™t had my dinner yet!</t>
-        </is>
-      </c>
+          <t>L2130: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L555: isolated marker/symbol line :: 3</t>
+          <t>L554: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -2067,7 +2067,11 @@
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>L2341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •chants' Despatch Transportation Çompany</t>
+        </is>
+      </c>
       <c r="T19" s="1" t="inlineStr"/>
       <c r="U19" s="1" t="inlineStr"/>
       <c r="V19" s="1" t="inlineStr">
@@ -2099,19 +2103,15 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L1073: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é…�</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+          <t>L2166: stray/suspicious non-ASCII glyph(s): U+52A0 CJK UNIFIED IDEOGRAPH-52A0 | isolated marker/symbol line :: 加</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: U</t>
+          <t>L555: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -2126,7 +2126,11 @@
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>L2575: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •9</t>
+        </is>
+      </c>
       <c r="T20" s="1" t="inlineStr"/>
       <c r="U20" s="1" t="inlineStr"/>
       <c r="V20" s="1" t="inlineStr">
@@ -2158,19 +2162,15 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L1163: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: b Ã© reached by sledging parties starting from</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: cutor, F. MacKelcan, J. E. Oâ€™Reilly, F.</t>
-        </is>
-      </c>
+          <t>L2180: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: 4</t>
+          <t>L578: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -2185,12 +2185,16 @@
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>L2686: line starts with punctuation glued to text :: * on the dollar, which is a guarantee that he</t>
+        </is>
+      </c>
       <c r="T21" s="1" t="inlineStr"/>
       <c r="U21" s="1" t="inlineStr"/>
       <c r="V21" s="1" t="inlineStr">
         <is>
-          <t>L1785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: MR. M. C.C.â€”I think sO, sir. (Reads.)</t>
+          <t>L1785: abbreviation/spacing may be garbled :: MR. M. C.C.—I think sO, sir. (Reads.)</t>
         </is>
       </c>
       <c r="W21" s="1" t="inlineStr"/>
@@ -2217,19 +2221,15 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ThurSday (odd internal casing) :: THE BISHOP OF NIAGARA.â€” On ThurSday the</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L203: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: constituencies and gained oneâ€”leaving a net</t>
-        </is>
-      </c>
+          <t>L2194: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: 755</t>
+          <t>L604: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2249,7 +2249,7 @@
       <c r="U22" s="1" t="inlineStr"/>
       <c r="V22" s="1" t="inlineStr">
         <is>
-          <t>L1798: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr. M.C.C.(Reads)Premierâ€”Mr. M.</t>
+          <t>L1798: abbreviation/spacing may be garbled :: Mr. M.C.C.(Reads)Premier—Mr. M.</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr"/>
@@ -2276,19 +2276,15 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L1272: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: It Never Failsï¼�ï¼�</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L243: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tins George Jamesâ€™ Old Stand,)-</t>
-        </is>
-      </c>
+          <t>L2195: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L607: isolated marker/symbol line :: S</t>
+          <t>L606: isolated marker/symbol line :: 755</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2299,7 +2295,7 @@
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L1640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----â€¢ ----</t>
+          <t>L1640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -----• ----</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2308,7 +2304,7 @@
       <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" s="1" t="inlineStr">
         <is>
-          <t>L1809: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr. M. C.C.(clears.his throat) â€œ.throat-</t>
+          <t>L1809: abbreviation/spacing may be garbled :: Mr. M. C.C.(clears.his throat) “.throat-</t>
         </is>
       </c>
       <c r="W23" s="1" t="inlineStr"/>
@@ -2333,26 +2329,18 @@
           <t>L1017: suspicious token(s): 25c (letter/digit mix) :: Price 25c. per packet Toronto.</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L1326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wheatâ€”Deihl...</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TASSO LINENâ€”(For Costumes)â€”from 15 cents.</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L608: isolated marker/symbol line :: 1</t>
+          <t>L607: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L1275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1275: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2392,21 +2380,13 @@
           <t>L1019: suspicious token(s): w20 (letter/digit mix) :: For Sale by Druggists and Storekeepers. w20-se</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L1327: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦$</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L253: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GENAPPINE CLOTHâ€”for Mourningâ€”32 and 35 cents.</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L609: isolated marker/symbol line :: 1</t>
+          <t>L608: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2451,21 +2431,13 @@
           <t>L1121: suspicious token(s): DeRussy (odd internal casing) :: Also Major-General DeRussy, U. S. A.; Capt.</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L1339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦â€¦</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L258: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LINEN COSTUMESâ€”$2.00, $2.65, $3.25, and $4.00.-</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L862: isolated marker/symbol line :: /</t>
+          <t>L609: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2506,26 +2478,18 @@
           <t>L1125: suspicious token(s): leavingacknowledged (very long joined token) :: leavingacknowledged the hospitality they had</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L1366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œFare</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L863: isolated marker/symbol line :: ,</t>
+          <t>L851: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L1677: isolated marker/symbol line :: r</t>
+          <t>L1640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -----• ----</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2561,26 +2525,18 @@
           <t>L1186: suspicious token(s): 6c (letter/digit mix), 7e (letter/digit mix), 9c (letter/digit mix), 10c (letter/digit mix) :: 6c. to 7e., and hind quarters at 9c. to 10c. per lb.</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L1382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BERLIN, June 8.â€”Wiesinger, who attempt-</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L941: symbol-only separator/garbage line :: $2, 324, 652.62.</t>
+          <t>L862: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L1697: isolated marker/symbol line :: 1</t>
+          <t>L1677: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2616,26 +2572,18 @@
           <t>L1187: suspicious token(s): 5c (letter/digit mix), 7c (letter/digit mix) :: Veal brought 5c. to 7c., and some particularly well</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L1383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LIVERPOOL, June 8.â€”The transatlantic</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L1073: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é…�</t>
+          <t>L863: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L1967: isolated marker/symbol line :: 20</t>
+          <t>L1697: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2671,26 +2619,18 @@
           <t>L1188: suspicious token(s): 8c (letter/digit mix) :: fed commanded 8c. per lb. There was a fine lot</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L1385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, June 8.â€”The Ascot meeting be-</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L1137: isolated marker/symbol line :: 4</t>
+          <t>L941: symbol-only separator/garbage line :: $2, 324, 652.62.</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L1969: isolated marker/symbol line :: 18</t>
+          <t>L1967: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2723,29 +2663,21 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 7c (letter/digit mix) :: of mutton offering from farmersâ€™ waggons at 7c.</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L1405: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L288: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BERLIN, June 8.â€”A grand banquet is to be</t>
-        </is>
-      </c>
+          <t>L1189: suspicious token(s): 7c (letter/digit mix) :: of mutton offering from farmers’ waggons at 7c.</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L1140: isolated marker/symbol line :: :</t>
+          <t>L1073: stray/suspicious non-ASCII glyph(s): U+914D CJK UNIFIED IDEOGRAPH-914D | isolated marker/symbol line :: 配</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L1971: isolated marker/symbol line :: 13</t>
+          <t>L1969: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2781,26 +2713,18 @@
           <t>L1190: suspicious token(s): 10c (letter/digit mix), 75c (letter/digit mix) :: to 10c. per lb. Lamb, by the quarter, sold at 75c.</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L1454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE DUNDAS Town. CLOCK.â€” We have re-</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DUBLIN, June 8.â€”The Lord Mayor of Dub-</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L1217: isolated marker/symbol line :: S</t>
+          <t>L1137: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L1973: symbol-only separator/garbage line :: 12]</t>
+          <t>L1971: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2836,26 +2760,18 @@
           <t>L1193: suspicious token(s): 22c (letter/digit mix) :: was 22c., but in some instances a little higher</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L1486: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the buildings were not set on fireâ€”we be-</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L1218: isolated marker/symbol line :: O</t>
+          <t>L1140: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L1975: isolated marker/symbol line :: 100</t>
+          <t>L1973: symbol-only separator/garbage line :: 12]</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2891,26 +2807,18 @@
           <t>L1194: suspicious token(s): 15c (letter/digit mix) :: price was paid. Eggs are getting scarce, at 15c.</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L1493: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the cabinet store of Heraldâ€™s pianofo</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L1226: symbol-only separator/garbage line :: 23-311 *</t>
+          <t>L1217: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L1976: isolated marker/symbol line :: 100</t>
+          <t>L1975: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2946,26 +2854,18 @@
           <t>L1209: suspicious token(s): 32c (letter/digit mix), 33c (letter/digit mix) :: willingly pay 32c. to 33c. per lb.</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L1546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FIRE.â€” A rather curious circumstance hap-</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: in the heat of the sunâ€”one of the glass</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L1241: isolated marker/symbol line :: V</t>
+          <t>L1218: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L2161: isolated marker/symbol line :: 03</t>
+          <t>L1976: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -3001,26 +2901,18 @@
           <t>L1229: suspicious token(s): 50c (letter/digit mix), 124c (letter/digit mix), 15c (letter/digit mix) :: at 50c. a dish. Eggs were from 124c. to 15c. a</t>
         </is>
       </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hat do you want, young man,â€”soft or stiff?"</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L1242: isolated marker/symbol line :: '</t>
+          <t>L1226: symbol-only separator/garbage line :: 23-311 *</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L2321: symbol-only separator/garbage line :: 4,854.</t>
+          <t>L2161: isolated marker/symbol line :: 03</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -3056,26 +2948,18 @@
           <t>L1233: suspicious token(s): 374c (letter/digit mix) :: price, and ranged as high as 374c. per pound. The</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L1630: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Coville. "Why don't you git a stiff â€˜un.</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L1243: isolated marker/symbol line :: -</t>
+          <t>L1241: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L2624: isolated marker/symbol line :: 1</t>
+          <t>L2321: symbol-only separator/garbage line :: 4,854.</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -3108,29 +2992,21 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>L1525: suspicious token(s): inForms (odd internal casing) :: inForms Â°f application can be obtained by apply-</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L1632: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: morrow morning.â€”Mail's report.</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L376: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bill?" whispered his surprised friend. â€œA</t>
-        </is>
-      </c>
+          <t>L1525: suspicious token(s): inForms (odd internal casing) :: inForms °f application can be obtained by apply-</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L1257: isolated marker/symbol line :: H</t>
+          <t>L1242: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L2729: isolated marker/symbol line :: -</t>
+          <t>L2575: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •9</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -3166,32 +3042,24 @@
           <t>L1575: suspicious token(s): w33 (letter/digit mix), 2i (letter/digit mix) :: w33-2i</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L1633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FIELD DAY â€” VISIT OF THE MINISTER OF MILITIA.</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: stiff â€˜un!" ejaculated Young Coville, staring</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L1258: isolated marker/symbol line :: S</t>
+          <t>L1243: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L2735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L2624: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L1726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mackerelâ€”each .......</t>
+          <t>L1726: punctuation artifact: repeated periods :: Mackerel—each .......</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -3221,26 +3089,18 @@
           <t>L1673: suspicious token(s): wl9 (letter/digit mix), 5i (letter/digit mix) :: brellas and parasols. wl9-5i*</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L1674: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OTTAWA, June 8.â€” It is proposed here to</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L378: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: contemptuously at his companion. â€œ Anâ€™</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L1267: isolated marker/symbol line :: .</t>
+          <t>L1257: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L2761: isolated marker/symbol line :: %</t>
+          <t>L2729: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -3276,26 +3136,18 @@
           <t>L1679: suspicious token(s): d26 (letter/digit mix) :: d26-mwf-ly w-eow-ly</t>
         </is>
       </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L1713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Jewish Synagogue â€”</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: silent.â€”Danbury News.</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L1320: isolated marker/symbol line :: G</t>
+          <t>L1258: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L2763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L2735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -3331,26 +3183,18 @@
           <t>L1701: punctuation artifact: repeated periods | suspicious token(s): 1b (letter/digit mix) :: Beef, fore quarter, per 1b.........</t>
         </is>
       </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L1715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ToRoNTo (odd internal casing) :: ToRoNTo, June 8.â€” The Jews of this city</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: be produced at Boothâ€™s Theatre somewhere in</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L1328: isolated marker/symbol line :: 95</t>
+          <t>L1267: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L2767: isolated marker/symbol line :: -</t>
+          <t>L2761: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -3386,26 +3230,18 @@
           <t>L1706: punctuation artifact: repeated periods | suspicious token(s): 1b (letter/digit mix) :: Mutton, hind quarter, per 1b...</t>
         </is>
       </c>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L1748: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr.M.C.C.â€”(Impassionately)â€”Well</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” SON Street. Although it is only a week since the above Mammoth Establishment was opened,</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L1331: isolated marker/symbol line :: 97</t>
+          <t>L1320: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L2769: isolated marker/symbol line :: -</t>
+          <t>L2763: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3441,24 +3277,20 @@
           <t>L1838: line starts with digit/letter garbage token | suspicious token(s): 3Cures (letter/digit mix) | candidate OCR token mismatch vs other OCR: "Cures" vs "3Cures" :: 3Cures all Nervous Diseases, such as</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L1751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GrIP (odd internal casing) :: GrIP â€” Come, no quoting from Too LE in my</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: beautiful stocks of Dry Goods, Millinery, Mantles, Carpets and General House Furnishing Go -â€”</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L1333: isolated marker/symbol line :: 95</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L1327: isolated marker/symbol line :: …$</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L2767: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr">
         <is>
@@ -3492,24 +3324,20 @@
           <t>L1856: suspicious token(s): Fu11particulars (letter/digit mix) :: special diseases. Fu11particulars in our pamphlet,</t>
         </is>
       </c>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L1759: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIP-ch â€” I am shocked to hear you speak in</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L459: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Dominion. Ladies will be pleased to find full stocks of Infantsâ€™ Clothing, and Missesâ€™ and</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L1335: isolated marker/symbol line :: 90</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L1328: isolated marker/symbol line :: 95</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L2769: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr">
         <is>
@@ -3543,21 +3371,13 @@
           <t>L1863: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 5WILLIAM (letter/digit mix) :: 5WILLIAM GRAY &amp; Co.,...</t>
         </is>
       </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L1764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. M. C. C.â€”(Confidentially) Come in</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L469: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pet Yarns cheap.â€”Millinery and Mantles made to order.â€”German Spoken.â€”Termsâ€”POSITI-</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L1336: isolated marker/symbol line :: 92</t>
+          <t>L1331: isolated marker/symbol line :: 97</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3594,21 +3414,13 @@
           <t>L1871: suspicious token(s): d121 (letter/digit mix), w21 (letter/digit mix), 1y (letter/digit mix) :: proprietors prices. d121-w21-1y cow</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L1778: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Grip (Facetiously)â€” Sheepskin? Ah, quite</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of the brideâ€™s father, John M. Henderson, Esq.,</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L1338: isolated marker/symbol line :: :</t>
+          <t>L1333: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3645,21 +3457,13 @@
           <t>L1878: suspicious token(s): McBRIER (odd internal casing) :: DER McBRIER, both individually and as a</t>
         </is>
       </c>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L1780: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. M. C. C.â€”(Reluctantly, and with a</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At the residence of the brideâ€™s father. No. 10</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L1340: isolated marker/symbol line :: 90</t>
+          <t>L1335: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3696,21 +3500,13 @@
           <t>L1879: suspicious token(s): McBRIER (odd internal casing) :: member of the firm of NISBET &amp; McBRIER</t>
         </is>
       </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L1781: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: slight blush, reads.)Attorney-Generalâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L542: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: HARTERY, of St. Johnâ€™s, Newfoundland, aged 66</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L1342: isolated marker/symbol line :: 95</t>
+          <t>L1336: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3747,21 +3543,13 @@
           <t>L2012: suspicious token(s): McBRIER (odd internal casing) :: ALEXANDER J. McBRIER,</t>
         </is>
       </c>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L1783: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIP-rest â€” Very good, so far; he's the best and</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L547: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: STONE â€”In this city, on Monday, the 7th inst.,</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L1344: isolated marker/symbol line :: 8</t>
+          <t>L1338: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3798,21 +3586,13 @@
           <t>L2017: suspicious token(s): w21 (letter/digit mix), 6i (letter/digit mix) :: w21-6i</t>
         </is>
       </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L1785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: MR. M. C.C.â€”I think sO, sir. (Reads.)</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L562: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 85 TO $20 PER DAY.â€”Agents Wanted</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L1345: isolated marker/symbol line :: 90</t>
+          <t>L1339: isolated marker/symbol line :: ………</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3849,21 +3629,13 @@
           <t>L2253: suspicious token(s): From1 (letter/digit mix) :: be paid at time of sale. From1 to 5 years will be</t>
         </is>
       </c>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L1786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œProvincial Secretary-HoN. WM. MAC-</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -PAâ€”All classes of young people, of</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L1347: isolated marker/symbol line :: 90</t>
+          <t>L1340: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3900,21 +3672,13 @@
           <t>L2288: suspicious token(s): 93c (letter/digit mix) :: WHEAT-Market heavy, at 93c cash for June ;</t>
         </is>
       </c>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L1788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIP.â€”Good again. Immense improve-</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Coopersâ€™ Strike-Fire-Base Ball-Sale</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: 00</t>
+          <t>L1342: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3943,7 +3707,7 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ThurSday (odd internal casing) :: THE BISHOP OF NIAGARA.â€” On ThurSday the</t>
+          <t>L1189: suspicious token(s): ThurSday (odd internal casing) :: THE BISHOP OF NIAGARA.— On ThurSday the</t>
         </is>
       </c>
       <c r="I54" s="1" t="inlineStr">
@@ -3951,21 +3715,13 @@
           <t>L2293: suspicious token(s): 684c (letter/digit mix), 69c (letter/digit mix), 72c (letter/digit mix) :: 684c. to 69c. for July; offered at 72c. for August;</t>
         </is>
       </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L1798: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr. M.C.C.(Reads)Premierâ€”Mr. M.</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of Cheeseâ€”Indian Depredation.</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L1351: isolated marker/symbol line :: 00</t>
+          <t>L1344: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -4002,21 +3758,13 @@
           <t>L2294: suspicious token(s): 67c (letter/digit mix) :: 67c bid for fresh.</t>
         </is>
       </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L1800: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GrIp (odd internal casing) :: GrIpâ€”Better still! I see you don't pro-</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PITTSBURG, June 8th.â€”Fifty journeymen</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L1357: symbol-only separator/garbage line :: 87046505</t>
+          <t>L1345: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -4050,24 +3798,16 @@
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>L2296: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: Oatsâ€”Market dull, 62c. for cash; 61c for</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L1809: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Mr. M. C.C.(clears.his throat) â€œ.throat-</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: St. Louis, June 8th.â€”A fire in the re-</t>
-        </is>
-      </c>
+          <t>L2296: suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: Oats—Market dull, 62c. for cash; 61c for</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L1358: isolated marker/symbol line :: 65</t>
+          <t>L1347: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -4104,21 +3844,13 @@
           <t>L2297: suspicious token(s): 574c (letter/digit mix), 578c (letter/digit mix), 424c (letter/digit mix) :: June; 574c to 578c for July; nominally 424c</t>
         </is>
       </c>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L1810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GRIp (odd internal casing) :: surer "â€”(An awkward pause â€” GRIp rings for</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Utica, N. Y., June 8th.â€”There were 3,500</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L1360: symbol-only separator/garbage line :: 127880</t>
+          <t>L1349: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -4152,24 +3884,16 @@
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>L2300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 34c (letter/digit mix), 31c (letter/digit mix) :: FREIGHTSâ€”Quiet. Asking 34c for wheat, 31c for</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L1812: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. C. moistens his lips and resumes)â€”)â€”</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Arapahoes made a descent on the horsesâ€™</t>
-        </is>
-      </c>
+          <t>L2300: suspicious token(s): 34c (letter/digit mix), 31c (letter/digit mix) :: FREIGHTS—Quiet. Asking 34c for wheat, 31c for</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L1361: symbol-only separator/garbage line :: 747888</t>
+          <t>L1351: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -4206,21 +3930,13 @@
           <t>L2301: suspicious token(s): 3c (letter/digit mix) :: corn, 3c for oats sail to Buffalo.</t>
         </is>
       </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L1813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Treasurer â€”(ahem 1) Mr. A. W. LAUDER."</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NEW York, June 8.â€”Arrived, steamship</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: 9</t>
+          <t>L1357: symbol-only separator/garbage line :: 87046505</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -4257,21 +3973,13 @@
           <t>L2309: suspicious token(s): 74c (letter/digit mix), 8c (letter/digit mix), 83c (letter/digit mix) :: 74c to 8c for cash ; nominally 83c July. Sales</t>
         </is>
       </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L1817: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIP â€”(Recovering his composure). Pray</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NEW York, June 8th.â€”The hundreth birth-</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L1367: isolated marker/symbol line :: 65</t>
+          <t>L1358: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -4305,24 +4013,16 @@
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>L2310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 11c (letter/digit mix), 114c (letter/digit mix) :: S. R.â€”11c. for cash; nominally 114c. for July;</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L1851: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASHESâ€”Market for for pots steady at $. 05 to</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L622: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WATERTOWN, N. Y., June 8.â€”William Par-</t>
-        </is>
-      </c>
+          <t>L2310: suspicious token(s): 11c (letter/digit mix), 114c (letter/digit mix) :: S. R.—11c. for cash; nominally 114c. for July;</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L1371: isolated marker/symbol line :: 4</t>
+          <t>L1360: symbol-only separator/garbage line :: 127880</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -4359,21 +4059,13 @@
           <t>L2324: suspicious token(s): 1i (letter/digit mix) :: 130-1i-w-23-21</t>
         </is>
       </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L1857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 87c (letter/digit mix), 663cfor (letter/digit mix) :: Corn-87c â€” Market dull and easier, at 663cfor June;</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L630: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WASHINGTON, June 8.â€”Probabilities: For</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L1373: isolated marker/symbol line :: 6</t>
+          <t>L1361: symbol-only separator/garbage line :: 747888</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -4410,21 +4102,13 @@
           <t>L2585: suspicious token(s): 10w (letter/digit mix), 10i (letter/digit mix) :: _ ______________________77-eod-10w 14-10i</t>
         </is>
       </c>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L1893: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BARLEYâ€”Nominal.</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NEW YORK, June 8.â€”The attendance of</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L1374: isolated marker/symbol line :: i</t>
+          <t>L1363: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -4453,29 +4137,21 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>L1305: suspicious token(s): sYRUP (odd internal casing) :: VIAN sYRUP (not Peruvian Bark ï¼‰ Sold by</t>
+          <t>L1305: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | suspicious token(s): sYRUP (odd internal casing) :: VIAN sYRUP (not Peruvian Bark ） Sold by</t>
         </is>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>L2628: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | suspicious token(s): 16c (letter/digit mix) :: â€˜COTTONâ€”Market heavy, at 16c. for middling</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L1971: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Thompson, Woodward, writes â€”" Send me</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and he said that Traceyâ€™s testimony is of the</t>
-        </is>
-      </c>
+          <t>L2628: suspicious token(s): 16c (letter/digit mix) :: ‘COTTON—Market heavy, at 16c. for middling</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L1375: isolated marker/symbol line :: 4</t>
+          <t>L1366: isolated marker/symbol line :: ………</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -4512,21 +4188,13 @@
           <t>L2647: suspicious token(s): 78c (letter/digit mix), 80c (letter/digit mix) :: 36,000 bushels, at 78c.to 80c, for steam western</t>
         </is>
       </c>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L2130: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Beecherâ€™s situation was needed.</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L1376: isolated marker/symbol line :: .</t>
+          <t>L1367: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -4563,21 +4231,13 @@
           <t>L2648: suspicious token(s): 80c (letter/digit mix), 83c (letter/digit mix) :: mixed ; 80c. to 83c. for sail do.</t>
         </is>
       </c>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L2162: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Heraldâ€™s Factory fell down with a crash;</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L1386: isolated marker/symbol line :: " 4</t>
+          <t>L1371: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -4614,21 +4274,13 @@
           <t>L2653: suspicious token(s): 70b (letter/digit mix), 724c (letter/digit mix) :: 38,000 bushels, at 70b. to 724c. for mixed west-</t>
         </is>
       </c>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L2174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L721: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tween 4 and 5 oâ€™clock a. m., when there was</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L1387: isolated marker/symbol line :: 66</t>
+          <t>L1373: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -4661,21 +4313,13 @@
           <t>L2654: suspicious token(s): 71c (letter/digit mix), 76c (letter/digit mix) :: ern ; 71c. to 76c. for white western.</t>
         </is>
       </c>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L2176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1y (letter/digit mix) :: â€”71-1y 95 King St. West.</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L1388: isolated marker/symbol line :: 46</t>
+          <t>L1374: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -4705,24 +4349,16 @@
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>L2658: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 13c (letter/digit mix), 16c (letter/digit mix) :: LARDâ€”13c. to 13-16c. for steam ; 14-c for kettle</t>
-        </is>
-      </c>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L2180: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢THOMA</t>
-        </is>
-      </c>
+          <t>L2658: suspicious token(s): 13c (letter/digit mix), 16c (letter/digit mix) :: LARD—13c. to 13-16c. for steam ; 14-c for kettle</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L1406: isolated marker/symbol line :: "</t>
+          <t>L1375: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -4755,21 +4391,13 @@
           <t>L2661: suspicious token(s): 14c (letter/digit mix), 18c (letter/digit mix), 20c (letter/digit mix) :: BUTTER-14c. to 18c. for State and Pa.; 20c. to</t>
         </is>
       </c>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L2181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Starling * at Port Dalhousie</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L1423: isolated marker/symbol line :: 000</t>
+          <t>L1376: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -4802,21 +4430,13 @@
           <t>L2662: suspicious token(s): 27c (letter/digit mix) :: 27c. for new do.X</t>
         </is>
       </c>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L2194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œStarlingâ€� was lying at the pier the man, who</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L1426: isolated marker/symbol line :: 0</t>
+          <t>L1382: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -4846,24 +4466,16 @@
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>L2663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 13PRTROLEUM (letter/digit mix), 63c (letter/digit mix), 131c (letter/digit mix) :: 13PRTROLEUMâ€”Crude, at 63c. ; refined, 131c. to</t>
-        </is>
-      </c>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L2195: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L852: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sented by the last Legislature.â€”Liberal.</t>
-        </is>
-      </c>
+          <t>L2663: suspicious token(s): 13PRTROLEUM (letter/digit mix), 63c (letter/digit mix), 131c (letter/digit mix) :: 13PRTROLEUM—Crude, at 63c. ; refined, 131c. to</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L1427: isolated marker/symbol line :: 10</t>
+          <t>L1383: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4896,21 +4508,13 @@
           <t>L2685: suspicious token(s): 75c (letter/digit mix) :: sold out to a purchaser of the whole for 75c.</t>
         </is>
       </c>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L2214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: OATSâ€”Market du dull, 62c. for cash; 61c for</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NIAGARA, June 6th.â€”Instruction of the</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L1430: isolated marker/symbol line :: 0</t>
+          <t>L1385: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4935,7 +4539,7 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>L1715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ToRoNTo (odd internal casing) :: ToRoNTo, June 8.â€” The Jews of this city</t>
+          <t>L1715: suspicious token(s): ToRoNTo (odd internal casing) :: ToRoNTo, June 8.— The Jews of this city</t>
         </is>
       </c>
       <c r="I74" s="1" t="inlineStr">
@@ -4943,21 +4547,13 @@
           <t>L2749: suspicious token(s): McLACHLAN (odd internal casing) :: 56-tts TENNANT &amp; McLACHLAN</t>
         </is>
       </c>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L2268: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ford, Thamesville, writes â€”" Send at once a.</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L899: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: KILLED BY THE CARS.â€”We learn that on</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L1431: isolated marker/symbol line :: 80</t>
+          <t>L1386: isolated marker/symbol line :: " 4</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4982,7 +4578,7 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>L1751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GrIP (odd internal casing) :: GrIP â€” Come, no quoting from Too LE in my</t>
+          <t>L1751: suspicious token(s): GrIP (odd internal casing) :: GrIP — Come, no quoting from Too LE in my</t>
         </is>
       </c>
       <c r="I75" s="1" t="inlineStr">
@@ -4991,16 +4587,12 @@
         </is>
       </c>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L986: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: but he had one failingâ€”he drank excessively.</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L1434: isolated marker/symbol line :: 18</t>
+          <t>L1387: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -5025,21 +4617,17 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>L1800: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GrIp (odd internal casing) :: GrIpâ€”Better still! I see you don't pro-</t>
+          <t>L1800: suspicious token(s): GrIp (odd internal casing) :: GrIp—Better still! I see you don't pro-</t>
         </is>
       </c>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L991: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE DUNDAS Tows CLOCK.â€”We have re-I</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L1436: isolated marker/symbol line :: 0</t>
+          <t>L1388: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -5069,16 +4657,12 @@
       </c>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: stating that â€˜it has four or five faces, and on</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L1437: isolated marker/symbol line :: 255</t>
+          <t>L1405: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -5103,21 +4687,17 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>L1810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GRIp (odd internal casing) :: surer "â€”(An awkward pause â€” GRIp rings for</t>
+          <t>L1810: suspicious token(s): GRIp (odd internal casing) :: surer "—(An awkward pause — GRIp rings for</t>
         </is>
       </c>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1093: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: As a gentleman, fishing near Penzance,â€˜</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L1440: isolated marker/symbol line :: 20</t>
+          <t>L1406: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -5147,16 +4727,12 @@
       </c>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1144: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Markâ€™s Church was strengthened at both</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L1442: isolated marker/symbol line :: 0</t>
+          <t>L1423: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -5186,16 +4762,12 @@
       </c>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sion of several members of the Queenâ€™s Own.</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L1444: isolated marker/symbol line :: 0</t>
+          <t>L1426: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -5225,16 +4797,12 @@
       </c>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1182: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: morrow morning.â€”Mailâ€™s report.</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L1445: isolated marker/symbol line :: 4</t>
+          <t>L1427: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -5264,16 +4832,12 @@
       </c>
       <c r="I82" s="1" t="inlineStr"/>
       <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1184: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FIELD DAYâ€”VISIT OF THE MINISTER OF MILITIA.</t>
-        </is>
-      </c>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L1450: isolated marker/symbol line :: X</t>
+          <t>L1430: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -5303,16 +4867,12 @@
       </c>
       <c r="I83" s="1" t="inlineStr"/>
       <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 7c (letter/digit mix) :: of mutton offering from farmersâ€™ waggons at 7c.</t>
-        </is>
-      </c>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L1455: isolated marker/symbol line :: S</t>
+          <t>L1431: isolated marker/symbol line :: 80</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -5337,21 +4897,17 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>L1857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 87c (letter/digit mix), 663cfor (letter/digit mix) :: Corn-87c â€” Market dull and easier, at 663cfor June;</t>
+          <t>L1857: suspicious token(s): 87c (letter/digit mix), 663cfor (letter/digit mix) :: Corn-87c — Market dull and easier, at 663cfor June;</t>
         </is>
       </c>
       <c r="I84" s="1" t="inlineStr"/>
       <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1225: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Meat Market remains unchanged, and alsoâ€”with</t>
-        </is>
-      </c>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L1459: isolated marker/symbol line :: 2</t>
+          <t>L1434: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -5381,16 +4937,12 @@
       </c>
       <c r="I85" s="1" t="inlineStr"/>
       <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pound dearerâ€”the same may be said of the Fish</t>
-        </is>
-      </c>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L1479: isolated marker/symbol line :: e</t>
+          <t>L1436: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -5420,16 +4972,12 @@
       </c>
       <c r="I86" s="1" t="inlineStr"/>
       <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L1480: isolated marker/symbol line :: 4</t>
+          <t>L1437: isolated marker/symbol line :: 255</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -5459,16 +5007,12 @@
       </c>
       <c r="I87" s="1" t="inlineStr"/>
       <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the Bank of Montrealâ€”Verdict-Ar-</t>
-        </is>
-      </c>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L1484: isolated marker/symbol line :: 22</t>
+          <t>L1440: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -5498,16 +5042,12 @@
       </c>
       <c r="I88" s="1" t="inlineStr"/>
       <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1285: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MONTREAL, June 8.â€”The annual meeting</t>
-        </is>
-      </c>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L1488: isolated marker/symbol line :: 64</t>
+          <t>L1442: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -5537,16 +5077,12 @@
       </c>
       <c r="I89" s="1" t="inlineStr"/>
       <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: On the doctorâ€™s report a verdict of infanticide</t>
-        </is>
-      </c>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L1489: isolated marker/symbol line :: 64</t>
+          <t>L1444: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -5576,16 +5112,12 @@
       </c>
       <c r="I90" s="1" t="inlineStr"/>
       <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1358: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to Hallâ€™s wretched little steamer, can reach a</t>
-        </is>
-      </c>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L1490: isolated marker/symbol line :: 20</t>
+          <t>L1445: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -5615,16 +5147,12 @@
       </c>
       <c r="I91" s="1" t="inlineStr"/>
       <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and to come.â€� Owing to the intense heat the</t>
-        </is>
-      </c>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L1492: symbol-only separator/garbage line :: 2525208</t>
+          <t>L1450: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -5654,16 +5182,12 @@
       </c>
       <c r="I92" s="1" t="inlineStr"/>
       <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L1389: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: .THE BISHOP OF NIAGARA.â€”On Thursday the</t>
-        </is>
-      </c>
+      <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L1496: isolated marker/symbol line :: 13</t>
+          <t>L1455: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -5693,16 +5217,12 @@
       </c>
       <c r="I93" s="1" t="inlineStr"/>
       <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L1405: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: in the project.â€”News.</t>
-        </is>
-      </c>
+      <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L1497: isolated marker/symbol line :: 0</t>
+          <t>L1459: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -5732,16 +5252,12 @@
       </c>
       <c r="I94" s="1" t="inlineStr"/>
       <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L1439: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TRIO OIL!â€”WORTH TEN TIMES ITS WEIGHT</t>
-        </is>
-      </c>
+      <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L1498: isolated marker/symbol line :: 00</t>
+          <t>L1479: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -5771,16 +5287,12 @@
       </c>
       <c r="I95" s="1" t="inlineStr"/>
       <c r="J95" s="1" t="inlineStr"/>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L1512: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” of Candidates for 2nd and 3rd Class Certi-</t>
-        </is>
-      </c>
+      <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L1500: isolated marker/symbol line :: 12</t>
+          <t>L1480: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -5810,16 +5322,12 @@
       </c>
       <c r="I96" s="1" t="inlineStr"/>
       <c r="J96" s="1" t="inlineStr"/>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L1555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Caution.â€”Be sure you get the as PERU.</t>
-        </is>
-      </c>
+      <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L1502: isolated marker/symbol line :: 15</t>
+          <t>L1484: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5849,16 +5357,12 @@
       </c>
       <c r="I97" s="1" t="inlineStr"/>
       <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L1556: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: VIAN SYRUPâ€� (not Peruvian Bark.) Sold by</t>
-        </is>
-      </c>
+      <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L1486: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5888,16 +5392,12 @@
       </c>
       <c r="I98" s="1" t="inlineStr"/>
       <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L1589: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Acres of Land,</t>
-        </is>
-      </c>
+      <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L1630: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L1488: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5927,16 +5427,12 @@
       </c>
       <c r="I99" s="1" t="inlineStr"/>
       <c r="J99" s="1" t="inlineStr"/>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: a half of Hallâ€™s Corners. Immediate possession</t>
-        </is>
-      </c>
+      <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L1697: isolated marker/symbol line :: ,</t>
+          <t>L1489: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5966,16 +5462,12 @@
       </c>
       <c r="I100" s="1" t="inlineStr"/>
       <c r="J100" s="1" t="inlineStr"/>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L1597: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WM, WEIGHT, Hallâ€™s Corners, Binbrook P. O.</t>
-        </is>
-      </c>
+      <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L1775: isolated marker/symbol line :: 4</t>
+          <t>L1490: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -6005,16 +5497,12 @@
       </c>
       <c r="I101" s="1" t="inlineStr"/>
       <c r="J101" s="1" t="inlineStr"/>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: , Wheatâ€”Deihl........</t>
-        </is>
-      </c>
+      <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L1833: isolated marker/symbol line :: 1</t>
+          <t>L1492: symbol-only separator/garbage line :: 2525208</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -6044,16 +5532,12 @@
       </c>
       <c r="I102" s="1" t="inlineStr"/>
       <c r="J102" s="1" t="inlineStr"/>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: COURT HOUSE CARE TAKER.â€”We learn that</t>
-        </is>
-      </c>
+      <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L1874: symbol-only separator/garbage line :: 4, 854.</t>
+          <t>L1493: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -6083,16 +5567,12 @@
       </c>
       <c r="I103" s="1" t="inlineStr"/>
       <c r="J103" s="1" t="inlineStr"/>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L1640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----â€¢ ----</t>
-        </is>
-      </c>
+      <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L1875: isolated marker/symbol line :: 2</t>
+          <t>L1496: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -6122,16 +5602,12 @@
       </c>
       <c r="I104" s="1" t="inlineStr"/>
       <c r="J104" s="1" t="inlineStr"/>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L1642: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE Chors.â€”Owing to the long continued</t>
-        </is>
-      </c>
+      <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L2056: isolated marker/symbol line :: 2</t>
+          <t>L1497: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -6161,16 +5637,12 @@
       </c>
       <c r="I105" s="1" t="inlineStr"/>
       <c r="J105" s="1" t="inlineStr"/>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L1655: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: INSECTS ON PLUS TREES.â€”Parties who may</t>
-        </is>
-      </c>
+      <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L2077: isolated marker/symbol line :: &amp;</t>
+          <t>L1498: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -6200,16 +5672,12 @@
       </c>
       <c r="I106" s="1" t="inlineStr"/>
       <c r="J106" s="1" t="inlineStr"/>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L1726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mackerelâ€”each .......</t>
-        </is>
-      </c>
+      <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L2078: isolated marker/symbol line :: &amp;</t>
+          <t>L1500: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -6239,16 +5707,12 @@
       </c>
       <c r="I107" s="1" t="inlineStr"/>
       <c r="J107" s="1" t="inlineStr"/>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L1764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ DR</t>
-        </is>
-      </c>
+      <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L2087: isolated marker/symbol line :: } O</t>
+          <t>L1502: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -6278,16 +5742,12 @@
       </c>
       <c r="I108" s="1" t="inlineStr"/>
       <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L1778: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”(Hesitatingly) â€”Ah, th-a-n-ks</t>
-        </is>
-      </c>
+      <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L2088: isolated marker/symbol line :: 0</t>
+          <t>L1629: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -6317,16 +5777,12 @@
       </c>
       <c r="I109" s="1" t="inlineStr"/>
       <c r="J109" s="1" t="inlineStr"/>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L1779: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”th-a-n-ks.</t>
-        </is>
-      </c>
+      <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L2089: isolated marker/symbol line :: N</t>
+          <t>L1630: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -6356,16 +5812,12 @@
       </c>
       <c r="I110" s="1" t="inlineStr"/>
       <c r="J110" s="1" t="inlineStr"/>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L1781: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”Now, between you and Mac. I look</t>
-        </is>
-      </c>
+      <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L2125: isolated marker/symbol line :: 4</t>
+          <t>L1697: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -6395,16 +5847,12 @@
       </c>
       <c r="I111" s="1" t="inlineStr"/>
       <c r="J111" s="1" t="inlineStr"/>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L1787: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€” (Impassionately) â€” We'll</t>
-        </is>
-      </c>
+      <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L2130: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
+          <t>L1775: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -6434,16 +5882,12 @@
       </c>
       <c r="I112" s="1" t="inlineStr"/>
       <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L1788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: attain them, too, by the Jingoâ€”we shall, by</t>
-        </is>
-      </c>
+      <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L2131: isolated marker/symbol line :: 100</t>
+          <t>L1833: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -6473,16 +5917,12 @@
       </c>
       <c r="I113" s="1" t="inlineStr"/>
       <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L1791: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”Come, no quoting from TOOLE in my</t>
-        </is>
-      </c>
+      <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L2132: isolated marker/symbol line :: t</t>
+          <t>L1835: stray/suspicious non-ASCII glyph(s): U+221A SQUARE ROOT | isolated marker/symbol line :: √</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -6512,16 +5952,12 @@
       </c>
       <c r="I114" s="1" t="inlineStr"/>
       <c r="J114" s="1" t="inlineStr"/>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L1797: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mr. M. C. C.â€”Youâ€™re shouting, I have!</t>
-        </is>
-      </c>
+      <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L2133: symbol-only separator/garbage line :: 1 50</t>
+          <t>L1874: symbol-only separator/garbage line :: 4, 854.</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -6551,16 +5987,12 @@
       </c>
       <c r="I115" s="1" t="inlineStr"/>
       <c r="J115" s="1" t="inlineStr"/>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L1801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”I am shocked to hear you speak in</t>
-        </is>
-      </c>
+      <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L2134: isolated marker/symbol line :: 100</t>
+          <t>L1875: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -6590,16 +6022,12 @@
       </c>
       <c r="I116" s="1" t="inlineStr"/>
       <c r="J116" s="1" t="inlineStr"/>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>L1807: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”(Confidentially) Come in</t>
-        </is>
-      </c>
+      <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L2135: symbol-only separator/garbage line :: 1 25</t>
+          <t>L2056: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -6629,16 +6057,12 @@
       </c>
       <c r="I117" s="1" t="inlineStr"/>
       <c r="J117" s="1" t="inlineStr"/>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>L1817: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”Come, hurry up,â€”I'm sincerely</t>
-        </is>
-      </c>
+      <c r="K117" s="1" t="inlineStr"/>
       <c r="L117" s="1" t="inlineStr"/>
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L2137: isolated marker/symbol line :: 25</t>
+          <t>L2077: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -6668,16 +6092,12 @@
       </c>
       <c r="I118" s="1" t="inlineStr"/>
       <c r="J118" s="1" t="inlineStr"/>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>L1818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: anxious to learn what youâ€™re " going to do</t>
-        </is>
-      </c>
+      <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L2139: isolated marker/symbol line :: 00</t>
+          <t>L2078: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -6707,16 +6127,12 @@
       </c>
       <c r="I119" s="1" t="inlineStr"/>
       <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>L1821: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. M. C. C.â€”Here they are. (Producing</t>
-        </is>
-      </c>
+      <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L2141: isolated marker/symbol line :: 02</t>
+          <t>L2087: isolated marker/symbol line :: } O</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -6746,16 +6162,12 @@
       </c>
       <c r="I120" s="1" t="inlineStr"/>
       <c r="J120" s="1" t="inlineStr"/>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>L1823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GRAYâ€™S</t>
-        </is>
-      </c>
+      <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L2142: isolated marker/symbol line :: 0</t>
+          <t>L2088: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -6785,16 +6197,12 @@
       </c>
       <c r="I121" s="1" t="inlineStr"/>
       <c r="J121" s="1" t="inlineStr"/>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>L1857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ which we desire to send free by mail to every one.</t>
-        </is>
-      </c>
+      <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L2144: isolated marker/symbol line :: 20</t>
+          <t>L2089: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -6824,16 +6232,12 @@
       </c>
       <c r="I122" s="1" t="inlineStr"/>
       <c r="J122" s="1" t="inlineStr"/>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>L1877: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _____â€” TER of ALEXAN-</t>
-        </is>
-      </c>
+      <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L2145: isolated marker/symbol line :: 00</t>
+          <t>L2125: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -6863,16 +6267,12 @@
       </c>
       <c r="I123" s="1" t="inlineStr"/>
       <c r="J123" s="1" t="inlineStr"/>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>L1885: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: EUROPEAN CORRESPONDENCE.â€”Rev. Hugh</t>
-        </is>
-      </c>
+      <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L2147: isolated marker/symbol line :: 10</t>
+          <t>L2130: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -6902,16 +6302,12 @@
       </c>
       <c r="I124" s="1" t="inlineStr"/>
       <c r="J124" s="1" t="inlineStr"/>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>L1903: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rev. gentlemanâ€™s graphic description of the</t>
-        </is>
-      </c>
+      <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L2149: isolated marker/symbol line :: 14</t>
+          <t>L2131: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -6936,21 +6332,17 @@
       <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr">
         <is>
-          <t>L2214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: OATSâ€”Market du dull, 62c. for cash; 61c for</t>
+          <t>L2214: suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: OATS—Market du dull, 62c. for cash; 61c for</t>
         </is>
       </c>
       <c r="I125" s="1" t="inlineStr"/>
       <c r="J125" s="1" t="inlineStr"/>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>L1945: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Spring Onions, per doz bâ€™chs</t>
-        </is>
-      </c>
+      <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L2151: isolated marker/symbol line :: 00</t>
+          <t>L2132: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -6980,16 +6372,12 @@
       </c>
       <c r="I126" s="1" t="inlineStr"/>
       <c r="J126" s="1" t="inlineStr"/>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>L2000: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ to 00</t>
-        </is>
-      </c>
+      <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L2154: isolated marker/symbol line :: 50</t>
+          <t>L2133: symbol-only separator/garbage line :: 1 50</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -7019,16 +6407,12 @@
       </c>
       <c r="I127" s="1" t="inlineStr"/>
       <c r="J127" s="1" t="inlineStr"/>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>L2024: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OTTAWA, June 8.â€”It is proposed here to</t>
-        </is>
-      </c>
+      <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L2156: symbol-only separator/garbage line :: 0815888205108</t>
+          <t>L2134: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -7058,16 +6442,12 @@
       </c>
       <c r="I128" s="1" t="inlineStr"/>
       <c r="J128" s="1" t="inlineStr"/>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>L2057: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: hundred dollars cash to St. Patrickâ€™s Church,</t>
-        </is>
-      </c>
+      <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L2157: isolated marker/symbol line :: 4</t>
+          <t>L2135: symbol-only separator/garbage line :: 1 25</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -7093,16 +6473,12 @@
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr"/>
       <c r="J129" s="1" t="inlineStr"/>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>L2076: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NIAGARA, June 7.â€”This has been quite a</t>
-        </is>
-      </c>
+      <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L2159: isolated marker/symbol line :: 15</t>
+          <t>L2137: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -7128,16 +6504,12 @@
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr"/>
       <c r="J130" s="1" t="inlineStr"/>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>L2153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: probably take place on Wednesday.â€”Mailâ€™s</t>
-        </is>
-      </c>
+      <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L2163: isolated marker/symbol line :: 15</t>
+          <t>L2139: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -7163,16 +6535,12 @@
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr"/>
       <c r="J131" s="1" t="inlineStr"/>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>L2252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TERMS:â€”One-third of the purchase money to</t>
-        </is>
-      </c>
+      <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L2165: isolated marker/symbol line :: 03</t>
+          <t>L2141: isolated marker/symbol line :: 02</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -7198,16 +6566,12 @@
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr"/>
       <c r="J132" s="1" t="inlineStr"/>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>L2260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Vendorsâ€™ Solicitors,</t>
-        </is>
-      </c>
+      <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L2168: isolated marker/symbol line :: 04</t>
+          <t>L2142: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -7233,16 +6597,12 @@
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr"/>
       <c r="J133" s="1" t="inlineStr"/>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>L2266: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FLOURâ€”Receipts 3700 barrels ; sales, 1500 barrels.</t>
-        </is>
-      </c>
+      <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L2170: symbol-only separator/garbage line :: 02 $</t>
+          <t>L2144: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -7268,16 +6628,12 @@
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr"/>
       <c r="J134" s="1" t="inlineStr"/>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>L2278: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRAINâ€”There were 16,000 bushels of No. 2 Mil-</t>
-        </is>
-      </c>
+      <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L2175: isolated marker/symbol line :: 66</t>
+          <t>L2145: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -7303,16 +6659,12 @@
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr"/>
       <c r="J135" s="1" t="inlineStr"/>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>L2281: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PROVISIONSâ€”Quiet.</t>
-        </is>
-      </c>
+      <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L2180: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L2147: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -7338,16 +6690,12 @@
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr"/>
       <c r="J136" s="1" t="inlineStr"/>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>L2283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASHESâ€”Market for pots steady at $5.05 to</t>
-        </is>
-      </c>
+      <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L2185: isolated marker/symbol line :: 20</t>
+          <t>L2149: isolated marker/symbol line :: 14</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -7373,16 +6721,12 @@
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr"/>
       <c r="J137" s="1" t="inlineStr"/>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>L2286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CHICAGO, June 8â€”noon.</t>
-        </is>
-      </c>
+      <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L2191: isolated marker/symbol line :: 3</t>
+          <t>L2151: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -7408,16 +6752,12 @@
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr"/>
       <c r="J138" s="1" t="inlineStr"/>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>L2292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CORNâ€”Market dull and easier, at 66-cfor June ; =</t>
-        </is>
-      </c>
+      <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L2194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L2154: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -7443,16 +6783,12 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr"/>
       <c r="J139" s="1" t="inlineStr"/>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>L2296: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 62c (letter/digit mix), 61c (letter/digit mix) :: Oatsâ€”Market dull, 62c. for cash; 61c for</t>
-        </is>
-      </c>
+      <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L2195: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L2156: symbol-only separator/garbage line :: 0815888205108</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -7478,16 +6814,12 @@
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr"/>
       <c r="J140" s="1" t="inlineStr"/>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>L2300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 34c (letter/digit mix), 31c (letter/digit mix) :: FREIGHTSâ€”Quiet. Asking 34c for wheat, 31c for</t>
-        </is>
-      </c>
+      <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L2196: isolated marker/symbol line :: 2</t>
+          <t>L2157: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -7513,16 +6845,12 @@
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr"/>
       <c r="J141" s="1" t="inlineStr"/>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>L2306: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WHISKEYâ€”Dull. Sales nominally at $1.17.</t>
-        </is>
-      </c>
+      <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L2224: isolated marker/symbol line :: 0</t>
+          <t>L2159: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -7548,16 +6876,12 @@
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr"/>
       <c r="J142" s="1" t="inlineStr"/>
-      <c r="K142" s="1" t="inlineStr">
-        <is>
-          <t>L2308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Meatsâ€”Market quiet and easy. Shoulders a</t>
-        </is>
-      </c>
+      <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L2228: isolated marker/symbol line :: T</t>
+          <t>L2162: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -7583,16 +6907,12 @@
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr"/>
       <c r="J143" s="1" t="inlineStr"/>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>L2310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 11c (letter/digit mix), 114c (letter/digit mix) :: S. R.â€”11c. for cash; nominally 114c. for July;</t>
-        </is>
-      </c>
+      <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L2231: isolated marker/symbol line :: -</t>
+          <t>L2163: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -7618,16 +6938,12 @@
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr"/>
       <c r="J144" s="1" t="inlineStr"/>
-      <c r="K144" s="1" t="inlineStr">
-        <is>
-          <t>L2311: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 11 c. for Aug.â€”all loose.</t>
-        </is>
-      </c>
+      <c r="K144" s="1" t="inlineStr"/>
       <c r="L144" s="1" t="inlineStr"/>
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L2235: isolated marker/symbol line :: B</t>
+          <t>L2165: isolated marker/symbol line :: 03</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -7653,16 +6969,12 @@
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr"/>
       <c r="J145" s="1" t="inlineStr"/>
-      <c r="K145" s="1" t="inlineStr">
-        <is>
-          <t>L2313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Porkâ€”Market quiet and steady, at $19.45 for</t>
-        </is>
-      </c>
+      <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L2284: isolated marker/symbol line :: 3</t>
+          <t>L2166: stray/suspicious non-ASCII glyph(s): U+52A0 CJK UNIFIED IDEOGRAPH-52A0 | isolated marker/symbol line :: 加</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -7688,16 +7000,12 @@
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr"/>
       <c r="J146" s="1" t="inlineStr"/>
-      <c r="K146" s="1" t="inlineStr">
-        <is>
-          <t>L2317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lardâ€”Market firmer, at F$13.40 to $13.45 for</t>
-        </is>
-      </c>
+      <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L2285: isolated marker/symbol line :: .</t>
+          <t>L2168: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -7723,14 +7031,14 @@
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr"/>
       <c r="J147" s="1" t="inlineStr"/>
-      <c r="K147" s="1" t="inlineStr">
-        <is>
-          <t>L2320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LIVE STOCKâ€”Receipts, hogs, 8,731 ; shipmentsâ€™</t>
-        </is>
-      </c>
+      <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
-      <c r="N147" s="1" t="inlineStr"/>
+      <c r="N147" s="1" t="inlineStr">
+        <is>
+          <t>L2170: symbol-only separator/garbage line :: 02 $</t>
+        </is>
+      </c>
       <c r="O147" s="1" t="inlineStr"/>
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr"/>
@@ -7754,14 +7062,14 @@
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
       <c r="J148" s="1" t="inlineStr"/>
-      <c r="K148" s="1" t="inlineStr">
-        <is>
-          <t>L2336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: IMPORTANT NOTICE TO CHEESE SHIPPERSâ€”</t>
-        </is>
-      </c>
+      <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
-      <c r="N148" s="1" t="inlineStr"/>
+      <c r="N148" s="1" t="inlineStr">
+        <is>
+          <t>L2174: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O148" s="1" t="inlineStr"/>
       <c r="P148" s="1" t="inlineStr"/>
       <c r="Q148" s="1" t="inlineStr"/>
@@ -7785,14 +7093,14 @@
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr"/>
       <c r="J149" s="1" t="inlineStr"/>
-      <c r="K149" s="1" t="inlineStr">
-        <is>
-          <t>L2337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quick Despatch.â€”On Tuesday, 18th ultimo,</t>
-        </is>
-      </c>
+      <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
-      <c r="N149" s="1" t="inlineStr"/>
+      <c r="N149" s="1" t="inlineStr">
+        <is>
+          <t>L2175: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
       <c r="O149" s="1" t="inlineStr"/>
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr"/>
@@ -7816,14 +7124,14 @@
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr"/>
       <c r="J150" s="1" t="inlineStr"/>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>L2341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢chants' Despatch Transportation Ã‡ompany</t>
-        </is>
-      </c>
+      <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
-      <c r="N150" s="1" t="inlineStr"/>
+      <c r="N150" s="1" t="inlineStr">
+        <is>
+          <t>L2176: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O150" s="1" t="inlineStr"/>
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr"/>
@@ -7847,14 +7155,14 @@
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr"/>
       <c r="J151" s="1" t="inlineStr"/>
-      <c r="K151" s="1" t="inlineStr">
-        <is>
-          <t>L2369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”(Facetiously)â€”Sheepskin? Ah, quite</t>
-        </is>
-      </c>
+      <c r="K151" s="1" t="inlineStr"/>
       <c r="L151" s="1" t="inlineStr"/>
       <c r="M151" s="1" t="inlineStr"/>
-      <c r="N151" s="1" t="inlineStr"/>
+      <c r="N151" s="1" t="inlineStr">
+        <is>
+          <t>L2180: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
       <c r="O151" s="1" t="inlineStr"/>
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr"/>
@@ -7878,14 +7186,14 @@
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
       <c r="J152" s="1" t="inlineStr"/>
-      <c r="K152" s="1" t="inlineStr">
-        <is>
-          <t>L2372: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MR. M. C. C.â€”(Reluctantly, and with a</t>
-        </is>
-      </c>
+      <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
-      <c r="N152" s="1" t="inlineStr"/>
+      <c r="N152" s="1" t="inlineStr">
+        <is>
+          <t>L2181: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O152" s="1" t="inlineStr"/>
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr"/>
@@ -7909,14 +7217,14 @@
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
       <c r="J153" s="1" t="inlineStr"/>
-      <c r="K153" s="1" t="inlineStr">
-        <is>
-          <t>L2373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: slight blush, reads.) â€” - Attorney-Generalâ€”</t>
-        </is>
-      </c>
+      <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
-      <c r="N153" s="1" t="inlineStr"/>
+      <c r="N153" s="1" t="inlineStr">
+        <is>
+          <t>L2183: isolated marker/symbol line :: · 4</t>
+        </is>
+      </c>
       <c r="O153" s="1" t="inlineStr"/>
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr"/>
@@ -7940,14 +7248,14 @@
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
       <c r="J154" s="1" t="inlineStr"/>
-      <c r="K154" s="1" t="inlineStr">
-        <is>
-          <t>L2376: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”Very good, so far; he's the best and</t>
-        </is>
-      </c>
+      <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
-      <c r="N154" s="1" t="inlineStr"/>
+      <c r="N154" s="1" t="inlineStr">
+        <is>
+          <t>L2185: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
       <c r="O154" s="1" t="inlineStr"/>
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr"/>
@@ -7971,14 +7279,14 @@
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
       <c r="J155" s="1" t="inlineStr"/>
-      <c r="K155" s="1" t="inlineStr">
-        <is>
-          <t>L2379: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”I think so, sir. (Reads.)</t>
-        </is>
-      </c>
+      <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
-      <c r="N155" s="1" t="inlineStr"/>
+      <c r="N155" s="1" t="inlineStr">
+        <is>
+          <t>L2191: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
       <c r="O155" s="1" t="inlineStr"/>
       <c r="P155" s="1" t="inlineStr"/>
       <c r="Q155" s="1" t="inlineStr"/>
@@ -8002,14 +7310,14 @@
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
       <c r="J156" s="1" t="inlineStr"/>
-      <c r="K156" s="1" t="inlineStr">
-        <is>
-          <t>L2380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Provincial Secretaryâ€”Hon. WM. MAC-</t>
-        </is>
-      </c>
+      <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
-      <c r="N156" s="1" t="inlineStr"/>
+      <c r="N156" s="1" t="inlineStr">
+        <is>
+          <t>L2194: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
       <c r="O156" s="1" t="inlineStr"/>
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr"/>
@@ -8033,14 +7341,14 @@
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
       <c r="J157" s="1" t="inlineStr"/>
-      <c r="K157" s="1" t="inlineStr">
-        <is>
-          <t>L2383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIP.â€”Good again. Immense improve-</t>
-        </is>
-      </c>
+      <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
-      <c r="N157" s="1" t="inlineStr"/>
+      <c r="N157" s="1" t="inlineStr">
+        <is>
+          <t>L2195: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
       <c r="O157" s="1" t="inlineStr"/>
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr"/>
@@ -8064,14 +7372,14 @@
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
       <c r="J158" s="1" t="inlineStr"/>
-      <c r="K158" s="1" t="inlineStr">
-        <is>
-          <t>L2386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: held that office before, didnâ€™t he, when he</t>
-        </is>
-      </c>
+      <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
-      <c r="N158" s="1" t="inlineStr"/>
+      <c r="N158" s="1" t="inlineStr">
+        <is>
+          <t>L2196: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O158" s="1" t="inlineStr"/>
       <c r="P158" s="1" t="inlineStr"/>
       <c r="Q158" s="1" t="inlineStr"/>
@@ -8095,14 +7403,14 @@
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
       <c r="J159" s="1" t="inlineStr"/>
-      <c r="K159" s="1" t="inlineStr">
-        <is>
-          <t>L2394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C. (Reads) "Premierâ€”Mr. M.</t>
-        </is>
-      </c>
+      <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
-      <c r="N159" s="1" t="inlineStr"/>
+      <c r="N159" s="1" t="inlineStr">
+        <is>
+          <t>L2224: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O159" s="1" t="inlineStr"/>
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr"/>
@@ -8126,14 +7434,14 @@
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr"/>
       <c r="J160" s="1" t="inlineStr"/>
-      <c r="K160" s="1" t="inlineStr">
-        <is>
-          <t>L2398: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GRIPâ€”Better still ! I see you donâ€™t pro-</t>
-        </is>
-      </c>
+      <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
-      <c r="N160" s="1" t="inlineStr"/>
+      <c r="N160" s="1" t="inlineStr">
+        <is>
+          <t>L2228: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O160" s="1" t="inlineStr"/>
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr"/>
@@ -8157,14 +7465,14 @@
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr"/>
       <c r="J161" s="1" t="inlineStr"/>
-      <c r="K161" s="1" t="inlineStr">
-        <is>
-          <t>L2400: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and WILLIE can run the House while youâ€™re</t>
-        </is>
-      </c>
+      <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
-      <c r="N161" s="1" t="inlineStr"/>
+      <c r="N161" s="1" t="inlineStr">
+        <is>
+          <t>L2231: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="O161" s="1" t="inlineStr"/>
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr"/>
@@ -8188,14 +7496,14 @@
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
       <c r="J162" s="1" t="inlineStr"/>
-      <c r="K162" s="1" t="inlineStr">
-        <is>
-          <t>L2402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: each other, I believe. Heâ€™ll bring in the</t>
-        </is>
-      </c>
+      <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
-      <c r="N162" s="1" t="inlineStr"/>
+      <c r="N162" s="1" t="inlineStr">
+        <is>
+          <t>L2235: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O162" s="1" t="inlineStr"/>
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr"/>
@@ -8219,14 +7527,14 @@
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
       <c r="J163" s="1" t="inlineStr"/>
-      <c r="K163" s="1" t="inlineStr">
-        <is>
-          <t>L2408: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: surer"â€”(An awkward pauseâ€”GRIP rings for</t>
-        </is>
-      </c>
+      <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
-      <c r="N163" s="1" t="inlineStr"/>
+      <c r="N163" s="1" t="inlineStr">
+        <is>
+          <t>L2284: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
       <c r="O163" s="1" t="inlineStr"/>
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr"/>
@@ -8250,14 +7558,14 @@
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr"/>
       <c r="J164" s="1" t="inlineStr"/>
-      <c r="K164" s="1" t="inlineStr">
-        <is>
-          <t>L2410: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. C. moistens his lips and resumes)â€”</t>
-        </is>
-      </c>
+      <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
-      <c r="N164" s="1" t="inlineStr"/>
+      <c r="N164" s="1" t="inlineStr">
+        <is>
+          <t>L2285: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
       <c r="O164" s="1" t="inlineStr"/>
       <c r="P164" s="1" t="inlineStr"/>
       <c r="Q164" s="1" t="inlineStr"/>
@@ -8270,1215 +7578,6 @@
       <c r="X164" s="1" t="inlineStr"/>
       <c r="Y164" s="1" t="inlineStr"/>
     </row>
-    <row r="165">
-      <c r="A165" s="1" t="inlineStr"/>
-      <c r="B165" s="1" t="inlineStr"/>
-      <c r="C165" s="1" t="inlineStr"/>
-      <c r="D165" s="1" t="inlineStr"/>
-      <c r="E165" s="1" t="inlineStr"/>
-      <c r="F165" s="1" t="inlineStr"/>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
-      <c r="J165" s="1" t="inlineStr"/>
-      <c r="K165" s="1" t="inlineStr">
-        <is>
-          <t>L2411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œf Treasurerâ€”(ahem !)â€”Mr. A. W. LAUDER."</t>
-        </is>
-      </c>
-      <c r="L165" s="1" t="inlineStr"/>
-      <c r="M165" s="1" t="inlineStr"/>
-      <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr"/>
-      <c r="P165" s="1" t="inlineStr"/>
-      <c r="Q165" s="1" t="inlineStr"/>
-      <c r="R165" s="1" t="inlineStr"/>
-      <c r="S165" s="1" t="inlineStr"/>
-      <c r="T165" s="1" t="inlineStr"/>
-      <c r="U165" s="1" t="inlineStr"/>
-      <c r="V165" s="1" t="inlineStr"/>
-      <c r="W165" s="1" t="inlineStr"/>
-      <c r="X165" s="1" t="inlineStr"/>
-      <c r="Y165" s="1" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="inlineStr"/>
-      <c r="B166" s="1" t="inlineStr"/>
-      <c r="C166" s="1" t="inlineStr"/>
-      <c r="D166" s="1" t="inlineStr"/>
-      <c r="E166" s="1" t="inlineStr"/>
-      <c r="F166" s="1" t="inlineStr"/>
-      <c r="G166" s="1" t="inlineStr"/>
-      <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr"/>
-      <c r="J166" s="1" t="inlineStr"/>
-      <c r="K166" s="1" t="inlineStr">
-        <is>
-          <t>L2416: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GRIPâ€”(Recovering his composure.) Pray</t>
-        </is>
-      </c>
-      <c r="L166" s="1" t="inlineStr"/>
-      <c r="M166" s="1" t="inlineStr"/>
-      <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr"/>
-      <c r="P166" s="1" t="inlineStr"/>
-      <c r="Q166" s="1" t="inlineStr"/>
-      <c r="R166" s="1" t="inlineStr"/>
-      <c r="S166" s="1" t="inlineStr"/>
-      <c r="T166" s="1" t="inlineStr"/>
-      <c r="U166" s="1" t="inlineStr"/>
-      <c r="V166" s="1" t="inlineStr"/>
-      <c r="W166" s="1" t="inlineStr"/>
-      <c r="X166" s="1" t="inlineStr"/>
-      <c r="Y166" s="1" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="inlineStr"/>
-      <c r="B167" s="1" t="inlineStr"/>
-      <c r="C167" s="1" t="inlineStr"/>
-      <c r="D167" s="1" t="inlineStr"/>
-      <c r="E167" s="1" t="inlineStr"/>
-      <c r="F167" s="1" t="inlineStr"/>
-      <c r="G167" s="1" t="inlineStr"/>
-      <c r="H167" s="1" t="inlineStr"/>
-      <c r="I167" s="1" t="inlineStr"/>
-      <c r="J167" s="1" t="inlineStr"/>
-      <c r="K167" s="1" t="inlineStr">
-        <is>
-          <t>L2420: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of Agriculture and Public Worksâ€”Mr. Chas.</t>
-        </is>
-      </c>
-      <c r="L167" s="1" t="inlineStr"/>
-      <c r="M167" s="1" t="inlineStr"/>
-      <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr"/>
-      <c r="P167" s="1" t="inlineStr"/>
-      <c r="Q167" s="1" t="inlineStr"/>
-      <c r="R167" s="1" t="inlineStr"/>
-      <c r="S167" s="1" t="inlineStr"/>
-      <c r="T167" s="1" t="inlineStr"/>
-      <c r="U167" s="1" t="inlineStr"/>
-      <c r="V167" s="1" t="inlineStr"/>
-      <c r="W167" s="1" t="inlineStr"/>
-      <c r="X167" s="1" t="inlineStr"/>
-      <c r="Y167" s="1" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="inlineStr"/>
-      <c r="B168" s="1" t="inlineStr"/>
-      <c r="C168" s="1" t="inlineStr"/>
-      <c r="D168" s="1" t="inlineStr"/>
-      <c r="E168" s="1" t="inlineStr"/>
-      <c r="F168" s="1" t="inlineStr"/>
-      <c r="G168" s="1" t="inlineStr"/>
-      <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr"/>
-      <c r="J168" s="1" t="inlineStr"/>
-      <c r="K168" s="1" t="inlineStr">
-        <is>
-          <t>L2430: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. M. C. C.â€”Well, of course, if it comes</t>
-        </is>
-      </c>
-      <c r="L168" s="1" t="inlineStr"/>
-      <c r="M168" s="1" t="inlineStr"/>
-      <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr"/>
-      <c r="P168" s="1" t="inlineStr"/>
-      <c r="Q168" s="1" t="inlineStr"/>
-      <c r="R168" s="1" t="inlineStr"/>
-      <c r="S168" s="1" t="inlineStr"/>
-      <c r="T168" s="1" t="inlineStr"/>
-      <c r="U168" s="1" t="inlineStr"/>
-      <c r="V168" s="1" t="inlineStr"/>
-      <c r="W168" s="1" t="inlineStr"/>
-      <c r="X168" s="1" t="inlineStr"/>
-      <c r="Y168" s="1" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="inlineStr"/>
-      <c r="B169" s="1" t="inlineStr"/>
-      <c r="C169" s="1" t="inlineStr"/>
-      <c r="D169" s="1" t="inlineStr"/>
-      <c r="E169" s="1" t="inlineStr"/>
-      <c r="F169" s="1" t="inlineStr"/>
-      <c r="G169" s="1" t="inlineStr"/>
-      <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr"/>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr">
-        <is>
-          <t>L2438: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Miles Alarm Till Co.â€™s</t>
-        </is>
-      </c>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr"/>
-      <c r="R169" s="1" t="inlineStr"/>
-      <c r="S169" s="1" t="inlineStr"/>
-      <c r="T169" s="1" t="inlineStr"/>
-      <c r="U169" s="1" t="inlineStr"/>
-      <c r="V169" s="1" t="inlineStr"/>
-      <c r="W169" s="1" t="inlineStr"/>
-      <c r="X169" s="1" t="inlineStr"/>
-      <c r="Y169" s="1" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="inlineStr"/>
-      <c r="B170" s="1" t="inlineStr"/>
-      <c r="C170" s="1" t="inlineStr"/>
-      <c r="D170" s="1" t="inlineStr"/>
-      <c r="E170" s="1" t="inlineStr"/>
-      <c r="F170" s="1" t="inlineStr"/>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr"/>
-      <c r="J170" s="1" t="inlineStr"/>
-      <c r="K170" s="1" t="inlineStr">
-        <is>
-          <t>L2480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: IN GOLD.â€”Pain cannot stay where it is used.</t>
-        </is>
-      </c>
-      <c r="L170" s="1" t="inlineStr"/>
-      <c r="M170" s="1" t="inlineStr"/>
-      <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr"/>
-      <c r="P170" s="1" t="inlineStr"/>
-      <c r="Q170" s="1" t="inlineStr"/>
-      <c r="R170" s="1" t="inlineStr"/>
-      <c r="S170" s="1" t="inlineStr"/>
-      <c r="T170" s="1" t="inlineStr"/>
-      <c r="U170" s="1" t="inlineStr"/>
-      <c r="V170" s="1" t="inlineStr"/>
-      <c r="W170" s="1" t="inlineStr"/>
-      <c r="X170" s="1" t="inlineStr"/>
-      <c r="Y170" s="1" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="inlineStr"/>
-      <c r="B171" s="1" t="inlineStr"/>
-      <c r="C171" s="1" t="inlineStr"/>
-      <c r="D171" s="1" t="inlineStr"/>
-      <c r="E171" s="1" t="inlineStr"/>
-      <c r="F171" s="1" t="inlineStr"/>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr"/>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr">
-        <is>
-          <t>L2498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: agent left, it acts like a charmâ€”it was</t>
-        </is>
-      </c>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr"/>
-      <c r="R171" s="1" t="inlineStr"/>
-      <c r="S171" s="1" t="inlineStr"/>
-      <c r="T171" s="1" t="inlineStr"/>
-      <c r="U171" s="1" t="inlineStr"/>
-      <c r="V171" s="1" t="inlineStr"/>
-      <c r="W171" s="1" t="inlineStr"/>
-      <c r="X171" s="1" t="inlineStr"/>
-      <c r="Y171" s="1" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr"/>
-      <c r="B172" s="1" t="inlineStr"/>
-      <c r="C172" s="1" t="inlineStr"/>
-      <c r="D172" s="1" t="inlineStr"/>
-      <c r="E172" s="1" t="inlineStr"/>
-      <c r="F172" s="1" t="inlineStr"/>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr"/>
-      <c r="J172" s="1" t="inlineStr"/>
-      <c r="K172" s="1" t="inlineStr">
-        <is>
-          <t>L2500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: H. Cole, of Iona, writes, â€œ please forward.</t>
-        </is>
-      </c>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr"/>
-      <c r="R172" s="1" t="inlineStr"/>
-      <c r="S172" s="1" t="inlineStr"/>
-      <c r="T172" s="1" t="inlineStr"/>
-      <c r="U172" s="1" t="inlineStr"/>
-      <c r="V172" s="1" t="inlineStr"/>
-      <c r="W172" s="1" t="inlineStr"/>
-      <c r="X172" s="1" t="inlineStr"/>
-      <c r="Y172" s="1" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr"/>
-      <c r="B173" s="1" t="inlineStr"/>
-      <c r="C173" s="1" t="inlineStr"/>
-      <c r="D173" s="1" t="inlineStr"/>
-      <c r="E173" s="1" t="inlineStr"/>
-      <c r="F173" s="1" t="inlineStr"/>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
-      <c r="I173" s="1" t="inlineStr"/>
-      <c r="J173" s="1" t="inlineStr"/>
-      <c r="K173" s="1" t="inlineStr">
-        <is>
-          <t>L2504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ford, Thamesville, writesâ€”" Send at once a</t>
-        </is>
-      </c>
-      <c r="L173" s="1" t="inlineStr"/>
-      <c r="M173" s="1" t="inlineStr"/>
-      <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr"/>
-      <c r="P173" s="1" t="inlineStr"/>
-      <c r="Q173" s="1" t="inlineStr"/>
-      <c r="R173" s="1" t="inlineStr"/>
-      <c r="S173" s="1" t="inlineStr"/>
-      <c r="T173" s="1" t="inlineStr"/>
-      <c r="U173" s="1" t="inlineStr"/>
-      <c r="V173" s="1" t="inlineStr"/>
-      <c r="W173" s="1" t="inlineStr"/>
-      <c r="X173" s="1" t="inlineStr"/>
-      <c r="Y173" s="1" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="inlineStr"/>
-      <c r="B174" s="1" t="inlineStr"/>
-      <c r="C174" s="1" t="inlineStr"/>
-      <c r="D174" s="1" t="inlineStr"/>
-      <c r="E174" s="1" t="inlineStr"/>
-      <c r="F174" s="1" t="inlineStr"/>
-      <c r="G174" s="1" t="inlineStr"/>
-      <c r="H174" s="1" t="inlineStr"/>
-      <c r="I174" s="1" t="inlineStr"/>
-      <c r="J174" s="1" t="inlineStr"/>
-      <c r="K174" s="1" t="inlineStr">
-        <is>
-          <t>L2508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Thompson, Woodward, writesâ€”" Send me</t>
-        </is>
-      </c>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr"/>
-      <c r="R174" s="1" t="inlineStr"/>
-      <c r="S174" s="1" t="inlineStr"/>
-      <c r="T174" s="1" t="inlineStr"/>
-      <c r="U174" s="1" t="inlineStr"/>
-      <c r="V174" s="1" t="inlineStr"/>
-      <c r="W174" s="1" t="inlineStr"/>
-      <c r="X174" s="1" t="inlineStr"/>
-      <c r="Y174" s="1" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="inlineStr"/>
-      <c r="B175" s="1" t="inlineStr"/>
-      <c r="C175" s="1" t="inlineStr"/>
-      <c r="D175" s="1" t="inlineStr"/>
-      <c r="E175" s="1" t="inlineStr"/>
-      <c r="F175" s="1" t="inlineStr"/>
-      <c r="G175" s="1" t="inlineStr"/>
-      <c r="H175" s="1" t="inlineStr"/>
-      <c r="I175" s="1" t="inlineStr"/>
-      <c r="J175" s="1" t="inlineStr"/>
-      <c r="K175" s="1" t="inlineStr">
-        <is>
-          <t>L2511: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Reed, Ulverton, P. Q., writeâ€”" The Eclectric</t>
-        </is>
-      </c>
-      <c r="L175" s="1" t="inlineStr"/>
-      <c r="M175" s="1" t="inlineStr"/>
-      <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr"/>
-      <c r="P175" s="1" t="inlineStr"/>
-      <c r="Q175" s="1" t="inlineStr"/>
-      <c r="R175" s="1" t="inlineStr"/>
-      <c r="S175" s="1" t="inlineStr"/>
-      <c r="T175" s="1" t="inlineStr"/>
-      <c r="U175" s="1" t="inlineStr"/>
-      <c r="V175" s="1" t="inlineStr"/>
-      <c r="W175" s="1" t="inlineStr"/>
-      <c r="X175" s="1" t="inlineStr"/>
-      <c r="Y175" s="1" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="inlineStr"/>
-      <c r="B176" s="1" t="inlineStr"/>
-      <c r="C176" s="1" t="inlineStr"/>
-      <c r="D176" s="1" t="inlineStr"/>
-      <c r="E176" s="1" t="inlineStr"/>
-      <c r="F176" s="1" t="inlineStr"/>
-      <c r="G176" s="1" t="inlineStr"/>
-      <c r="H176" s="1" t="inlineStr"/>
-      <c r="I176" s="1" t="inlineStr"/>
-      <c r="J176" s="1" t="inlineStr"/>
-      <c r="K176" s="1" t="inlineStr">
-        <is>
-          <t>L2515: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Buckingham, P. Q., writeâ€”" Send us one</t>
-        </is>
-      </c>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr"/>
-      <c r="R176" s="1" t="inlineStr"/>
-      <c r="S176" s="1" t="inlineStr"/>
-      <c r="T176" s="1" t="inlineStr"/>
-      <c r="U176" s="1" t="inlineStr"/>
-      <c r="V176" s="1" t="inlineStr"/>
-      <c r="W176" s="1" t="inlineStr"/>
-      <c r="X176" s="1" t="inlineStr"/>
-      <c r="Y176" s="1" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr"/>
-      <c r="B177" s="1" t="inlineStr"/>
-      <c r="C177" s="1" t="inlineStr"/>
-      <c r="D177" s="1" t="inlineStr"/>
-      <c r="E177" s="1" t="inlineStr"/>
-      <c r="F177" s="1" t="inlineStr"/>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr"/>
-      <c r="J177" s="1" t="inlineStr"/>
-      <c r="K177" s="1" t="inlineStr">
-        <is>
-          <t>L2526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTEâ€”Eclectricâ€”Selected and Electrized.</t>
-        </is>
-      </c>
-      <c r="L177" s="1" t="inlineStr"/>
-      <c r="M177" s="1" t="inlineStr"/>
-      <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr"/>
-      <c r="P177" s="1" t="inlineStr"/>
-      <c r="Q177" s="1" t="inlineStr"/>
-      <c r="R177" s="1" t="inlineStr"/>
-      <c r="S177" s="1" t="inlineStr"/>
-      <c r="T177" s="1" t="inlineStr"/>
-      <c r="U177" s="1" t="inlineStr"/>
-      <c r="V177" s="1" t="inlineStr"/>
-      <c r="W177" s="1" t="inlineStr"/>
-      <c r="X177" s="1" t="inlineStr"/>
-      <c r="Y177" s="1" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="inlineStr"/>
-      <c r="B178" s="1" t="inlineStr"/>
-      <c r="C178" s="1" t="inlineStr"/>
-      <c r="D178" s="1" t="inlineStr"/>
-      <c r="E178" s="1" t="inlineStr"/>
-      <c r="F178" s="1" t="inlineStr"/>
-      <c r="G178" s="1" t="inlineStr"/>
-      <c r="H178" s="1" t="inlineStr"/>
-      <c r="I178" s="1" t="inlineStr"/>
-      <c r="J178" s="1" t="inlineStr"/>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>L2532: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Jewish Synagogueâ€”Remanded-</t>
-        </is>
-      </c>
-      <c r="L178" s="1" t="inlineStr"/>
-      <c r="M178" s="1" t="inlineStr"/>
-      <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr"/>
-      <c r="P178" s="1" t="inlineStr"/>
-      <c r="Q178" s="1" t="inlineStr"/>
-      <c r="R178" s="1" t="inlineStr"/>
-      <c r="S178" s="1" t="inlineStr"/>
-      <c r="T178" s="1" t="inlineStr"/>
-      <c r="U178" s="1" t="inlineStr"/>
-      <c r="V178" s="1" t="inlineStr"/>
-      <c r="W178" s="1" t="inlineStr"/>
-      <c r="X178" s="1" t="inlineStr"/>
-      <c r="Y178" s="1" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="inlineStr"/>
-      <c r="B179" s="1" t="inlineStr"/>
-      <c r="C179" s="1" t="inlineStr"/>
-      <c r="D179" s="1" t="inlineStr"/>
-      <c r="E179" s="1" t="inlineStr"/>
-      <c r="F179" s="1" t="inlineStr"/>
-      <c r="G179" s="1" t="inlineStr"/>
-      <c r="H179" s="1" t="inlineStr"/>
-      <c r="I179" s="1" t="inlineStr"/>
-      <c r="J179" s="1" t="inlineStr"/>
-      <c r="K179" s="1" t="inlineStr">
-        <is>
-          <t>L2544: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TORONTO, June 8.â€”The Jews of this city</t>
-        </is>
-      </c>
-      <c r="L179" s="1" t="inlineStr"/>
-      <c r="M179" s="1" t="inlineStr"/>
-      <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr"/>
-      <c r="P179" s="1" t="inlineStr"/>
-      <c r="Q179" s="1" t="inlineStr"/>
-      <c r="R179" s="1" t="inlineStr"/>
-      <c r="S179" s="1" t="inlineStr"/>
-      <c r="T179" s="1" t="inlineStr"/>
-      <c r="U179" s="1" t="inlineStr"/>
-      <c r="V179" s="1" t="inlineStr"/>
-      <c r="W179" s="1" t="inlineStr"/>
-      <c r="X179" s="1" t="inlineStr"/>
-      <c r="Y179" s="1" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="inlineStr"/>
-      <c r="B180" s="1" t="inlineStr"/>
-      <c r="C180" s="1" t="inlineStr"/>
-      <c r="D180" s="1" t="inlineStr"/>
-      <c r="E180" s="1" t="inlineStr"/>
-      <c r="F180" s="1" t="inlineStr"/>
-      <c r="G180" s="1" t="inlineStr"/>
-      <c r="H180" s="1" t="inlineStr"/>
-      <c r="I180" s="1" t="inlineStr"/>
-      <c r="J180" s="1" t="inlineStr"/>
-      <c r="K180" s="1" t="inlineStr">
-        <is>
-          <t>L2575: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢9</t>
-        </is>
-      </c>
-      <c r="L180" s="1" t="inlineStr"/>
-      <c r="M180" s="1" t="inlineStr"/>
-      <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr"/>
-      <c r="P180" s="1" t="inlineStr"/>
-      <c r="Q180" s="1" t="inlineStr"/>
-      <c r="R180" s="1" t="inlineStr"/>
-      <c r="S180" s="1" t="inlineStr"/>
-      <c r="T180" s="1" t="inlineStr"/>
-      <c r="U180" s="1" t="inlineStr"/>
-      <c r="V180" s="1" t="inlineStr"/>
-      <c r="W180" s="1" t="inlineStr"/>
-      <c r="X180" s="1" t="inlineStr"/>
-      <c r="Y180" s="1" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="inlineStr"/>
-      <c r="B181" s="1" t="inlineStr"/>
-      <c r="C181" s="1" t="inlineStr"/>
-      <c r="D181" s="1" t="inlineStr"/>
-      <c r="E181" s="1" t="inlineStr"/>
-      <c r="F181" s="1" t="inlineStr"/>
-      <c r="G181" s="1" t="inlineStr"/>
-      <c r="H181" s="1" t="inlineStr"/>
-      <c r="I181" s="1" t="inlineStr"/>
-      <c r="J181" s="1" t="inlineStr"/>
-      <c r="K181" s="1" t="inlineStr">
-        <is>
-          <t>L2591: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sixth day of JUNE, next, at the Sheriffâ€™s Office</t>
-        </is>
-      </c>
-      <c r="L181" s="1" t="inlineStr"/>
-      <c r="M181" s="1" t="inlineStr"/>
-      <c r="N181" s="1" t="inlineStr"/>
-      <c r="O181" s="1" t="inlineStr"/>
-      <c r="P181" s="1" t="inlineStr"/>
-      <c r="Q181" s="1" t="inlineStr"/>
-      <c r="R181" s="1" t="inlineStr"/>
-      <c r="S181" s="1" t="inlineStr"/>
-      <c r="T181" s="1" t="inlineStr"/>
-      <c r="U181" s="1" t="inlineStr"/>
-      <c r="V181" s="1" t="inlineStr"/>
-      <c r="W181" s="1" t="inlineStr"/>
-      <c r="X181" s="1" t="inlineStr"/>
-      <c r="Y181" s="1" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="inlineStr"/>
-      <c r="B182" s="1" t="inlineStr"/>
-      <c r="C182" s="1" t="inlineStr"/>
-      <c r="D182" s="1" t="inlineStr"/>
-      <c r="E182" s="1" t="inlineStr"/>
-      <c r="F182" s="1" t="inlineStr"/>
-      <c r="G182" s="1" t="inlineStr"/>
-      <c r="H182" s="1" t="inlineStr"/>
-      <c r="I182" s="1" t="inlineStr"/>
-      <c r="J182" s="1" t="inlineStr"/>
-      <c r="K182" s="1" t="inlineStr">
-        <is>
-          <t>L2628: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | suspicious token(s): 16c (letter/digit mix) :: â€˜COTTONâ€”Market heavy, at 16c. for middling</t>
-        </is>
-      </c>
-      <c r="L182" s="1" t="inlineStr"/>
-      <c r="M182" s="1" t="inlineStr"/>
-      <c r="N182" s="1" t="inlineStr"/>
-      <c r="O182" s="1" t="inlineStr"/>
-      <c r="P182" s="1" t="inlineStr"/>
-      <c r="Q182" s="1" t="inlineStr"/>
-      <c r="R182" s="1" t="inlineStr"/>
-      <c r="S182" s="1" t="inlineStr"/>
-      <c r="T182" s="1" t="inlineStr"/>
-      <c r="U182" s="1" t="inlineStr"/>
-      <c r="V182" s="1" t="inlineStr"/>
-      <c r="W182" s="1" t="inlineStr"/>
-      <c r="X182" s="1" t="inlineStr"/>
-      <c r="Y182" s="1" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="1" t="inlineStr"/>
-      <c r="B183" s="1" t="inlineStr"/>
-      <c r="C183" s="1" t="inlineStr"/>
-      <c r="D183" s="1" t="inlineStr"/>
-      <c r="E183" s="1" t="inlineStr"/>
-      <c r="F183" s="1" t="inlineStr"/>
-      <c r="G183" s="1" t="inlineStr"/>
-      <c r="H183" s="1" t="inlineStr"/>
-      <c r="I183" s="1" t="inlineStr"/>
-      <c r="J183" s="1" t="inlineStr"/>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>L2631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FLOURâ€”Dull. Receipts, 12,000 barrels ; sales,</t>
-        </is>
-      </c>
-      <c r="L183" s="1" t="inlineStr"/>
-      <c r="M183" s="1" t="inlineStr"/>
-      <c r="N183" s="1" t="inlineStr"/>
-      <c r="O183" s="1" t="inlineStr"/>
-      <c r="P183" s="1" t="inlineStr"/>
-      <c r="Q183" s="1" t="inlineStr"/>
-      <c r="R183" s="1" t="inlineStr"/>
-      <c r="S183" s="1" t="inlineStr"/>
-      <c r="T183" s="1" t="inlineStr"/>
-      <c r="U183" s="1" t="inlineStr"/>
-      <c r="V183" s="1" t="inlineStr"/>
-      <c r="W183" s="1" t="inlineStr"/>
-      <c r="X183" s="1" t="inlineStr"/>
-      <c r="Y183" s="1" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="1" t="inlineStr"/>
-      <c r="B184" s="1" t="inlineStr"/>
-      <c r="C184" s="1" t="inlineStr"/>
-      <c r="D184" s="1" t="inlineStr"/>
-      <c r="E184" s="1" t="inlineStr"/>
-      <c r="F184" s="1" t="inlineStr"/>
-      <c r="G184" s="1" t="inlineStr"/>
-      <c r="H184" s="1" t="inlineStr"/>
-      <c r="I184" s="1" t="inlineStr"/>
-      <c r="J184" s="1" t="inlineStr"/>
-      <c r="K184" s="1" t="inlineStr">
-        <is>
-          <t>L2634: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: RYE FLOURâ€”Quiet, without decided change.</t>
-        </is>
-      </c>
-      <c r="L184" s="1" t="inlineStr"/>
-      <c r="M184" s="1" t="inlineStr"/>
-      <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr"/>
-      <c r="P184" s="1" t="inlineStr"/>
-      <c r="Q184" s="1" t="inlineStr"/>
-      <c r="R184" s="1" t="inlineStr"/>
-      <c r="S184" s="1" t="inlineStr"/>
-      <c r="T184" s="1" t="inlineStr"/>
-      <c r="U184" s="1" t="inlineStr"/>
-      <c r="V184" s="1" t="inlineStr"/>
-      <c r="W184" s="1" t="inlineStr"/>
-      <c r="X184" s="1" t="inlineStr"/>
-      <c r="Y184" s="1" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="1" t="inlineStr"/>
-      <c r="B185" s="1" t="inlineStr"/>
-      <c r="C185" s="1" t="inlineStr"/>
-      <c r="D185" s="1" t="inlineStr"/>
-      <c r="E185" s="1" t="inlineStr"/>
-      <c r="F185" s="1" t="inlineStr"/>
-      <c r="G185" s="1" t="inlineStr"/>
-      <c r="H185" s="1" t="inlineStr"/>
-      <c r="I185" s="1" t="inlineStr"/>
-      <c r="J185" s="1" t="inlineStr"/>
-      <c r="K185" s="1" t="inlineStr">
-        <is>
-          <t>L2643: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Rteâ€”Market quiet. Receipts 9,000 bushels ;</t>
-        </is>
-      </c>
-      <c r="L185" s="1" t="inlineStr"/>
-      <c r="M185" s="1" t="inlineStr"/>
-      <c r="N185" s="1" t="inlineStr"/>
-      <c r="O185" s="1" t="inlineStr"/>
-      <c r="P185" s="1" t="inlineStr"/>
-      <c r="Q185" s="1" t="inlineStr"/>
-      <c r="R185" s="1" t="inlineStr"/>
-      <c r="S185" s="1" t="inlineStr"/>
-      <c r="T185" s="1" t="inlineStr"/>
-      <c r="U185" s="1" t="inlineStr"/>
-      <c r="V185" s="1" t="inlineStr"/>
-      <c r="W185" s="1" t="inlineStr"/>
-      <c r="X185" s="1" t="inlineStr"/>
-      <c r="Y185" s="1" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="1" t="inlineStr"/>
-      <c r="B186" s="1" t="inlineStr"/>
-      <c r="C186" s="1" t="inlineStr"/>
-      <c r="D186" s="1" t="inlineStr"/>
-      <c r="E186" s="1" t="inlineStr"/>
-      <c r="F186" s="1" t="inlineStr"/>
-      <c r="G186" s="1" t="inlineStr"/>
-      <c r="H186" s="1" t="inlineStr"/>
-      <c r="I186" s="1" t="inlineStr"/>
-      <c r="J186" s="1" t="inlineStr"/>
-      <c r="K186" s="1" t="inlineStr">
-        <is>
-          <t>L2646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CORNâ€”Quiet. Receipts, 85,000 bushels ; sales,</t>
-        </is>
-      </c>
-      <c r="L186" s="1" t="inlineStr"/>
-      <c r="M186" s="1" t="inlineStr"/>
-      <c r="N186" s="1" t="inlineStr"/>
-      <c r="O186" s="1" t="inlineStr"/>
-      <c r="P186" s="1" t="inlineStr"/>
-      <c r="Q186" s="1" t="inlineStr"/>
-      <c r="R186" s="1" t="inlineStr"/>
-      <c r="S186" s="1" t="inlineStr"/>
-      <c r="T186" s="1" t="inlineStr"/>
-      <c r="U186" s="1" t="inlineStr"/>
-      <c r="V186" s="1" t="inlineStr"/>
-      <c r="W186" s="1" t="inlineStr"/>
-      <c r="X186" s="1" t="inlineStr"/>
-      <c r="Y186" s="1" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="1" t="inlineStr"/>
-      <c r="B187" s="1" t="inlineStr"/>
-      <c r="C187" s="1" t="inlineStr"/>
-      <c r="D187" s="1" t="inlineStr"/>
-      <c r="E187" s="1" t="inlineStr"/>
-      <c r="F187" s="1" t="inlineStr"/>
-      <c r="G187" s="1" t="inlineStr"/>
-      <c r="H187" s="1" t="inlineStr"/>
-      <c r="I187" s="1" t="inlineStr"/>
-      <c r="J187" s="1" t="inlineStr"/>
-      <c r="K187" s="1" t="inlineStr">
-        <is>
-          <t>L2652: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OATSâ€”Steady. Receipts, 44,000 bushels; sales,</t>
-        </is>
-      </c>
-      <c r="L187" s="1" t="inlineStr"/>
-      <c r="M187" s="1" t="inlineStr"/>
-      <c r="N187" s="1" t="inlineStr"/>
-      <c r="O187" s="1" t="inlineStr"/>
-      <c r="P187" s="1" t="inlineStr"/>
-      <c r="Q187" s="1" t="inlineStr"/>
-      <c r="R187" s="1" t="inlineStr"/>
-      <c r="S187" s="1" t="inlineStr"/>
-      <c r="T187" s="1" t="inlineStr"/>
-      <c r="U187" s="1" t="inlineStr"/>
-      <c r="V187" s="1" t="inlineStr"/>
-      <c r="W187" s="1" t="inlineStr"/>
-      <c r="X187" s="1" t="inlineStr"/>
-      <c r="Y187" s="1" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="1" t="inlineStr"/>
-      <c r="B188" s="1" t="inlineStr"/>
-      <c r="C188" s="1" t="inlineStr"/>
-      <c r="D188" s="1" t="inlineStr"/>
-      <c r="E188" s="1" t="inlineStr"/>
-      <c r="F188" s="1" t="inlineStr"/>
-      <c r="G188" s="1" t="inlineStr"/>
-      <c r="H188" s="1" t="inlineStr"/>
-      <c r="I188" s="1" t="inlineStr"/>
-      <c r="J188" s="1" t="inlineStr"/>
-      <c r="K188" s="1" t="inlineStr">
-        <is>
-          <t>L2656: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PORKâ€”At $20.00 for new mess.</t>
-        </is>
-      </c>
-      <c r="L188" s="1" t="inlineStr"/>
-      <c r="M188" s="1" t="inlineStr"/>
-      <c r="N188" s="1" t="inlineStr"/>
-      <c r="O188" s="1" t="inlineStr"/>
-      <c r="P188" s="1" t="inlineStr"/>
-      <c r="Q188" s="1" t="inlineStr"/>
-      <c r="R188" s="1" t="inlineStr"/>
-      <c r="S188" s="1" t="inlineStr"/>
-      <c r="T188" s="1" t="inlineStr"/>
-      <c r="U188" s="1" t="inlineStr"/>
-      <c r="V188" s="1" t="inlineStr"/>
-      <c r="W188" s="1" t="inlineStr"/>
-      <c r="X188" s="1" t="inlineStr"/>
-      <c r="Y188" s="1" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="1" t="inlineStr"/>
-      <c r="B189" s="1" t="inlineStr"/>
-      <c r="C189" s="1" t="inlineStr"/>
-      <c r="D189" s="1" t="inlineStr"/>
-      <c r="E189" s="1" t="inlineStr"/>
-      <c r="F189" s="1" t="inlineStr"/>
-      <c r="G189" s="1" t="inlineStr"/>
-      <c r="H189" s="1" t="inlineStr"/>
-      <c r="I189" s="1" t="inlineStr"/>
-      <c r="J189" s="1" t="inlineStr"/>
-      <c r="K189" s="1" t="inlineStr">
-        <is>
-          <t>L2658: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 13c (letter/digit mix), 16c (letter/digit mix) :: LARDâ€”13c. to 13-16c. for steam ; 14-c for kettle</t>
-        </is>
-      </c>
-      <c r="L189" s="1" t="inlineStr"/>
-      <c r="M189" s="1" t="inlineStr"/>
-      <c r="N189" s="1" t="inlineStr"/>
-      <c r="O189" s="1" t="inlineStr"/>
-      <c r="P189" s="1" t="inlineStr"/>
-      <c r="Q189" s="1" t="inlineStr"/>
-      <c r="R189" s="1" t="inlineStr"/>
-      <c r="S189" s="1" t="inlineStr"/>
-      <c r="T189" s="1" t="inlineStr"/>
-      <c r="U189" s="1" t="inlineStr"/>
-      <c r="V189" s="1" t="inlineStr"/>
-      <c r="W189" s="1" t="inlineStr"/>
-      <c r="X189" s="1" t="inlineStr"/>
-      <c r="Y189" s="1" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="1" t="inlineStr"/>
-      <c r="B190" s="1" t="inlineStr"/>
-      <c r="C190" s="1" t="inlineStr"/>
-      <c r="D190" s="1" t="inlineStr"/>
-      <c r="E190" s="1" t="inlineStr"/>
-      <c r="F190" s="1" t="inlineStr"/>
-      <c r="G190" s="1" t="inlineStr"/>
-      <c r="H190" s="1" t="inlineStr"/>
-      <c r="I190" s="1" t="inlineStr"/>
-      <c r="J190" s="1" t="inlineStr"/>
-      <c r="K190" s="1" t="inlineStr">
-        <is>
-          <t>L2663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 13PRTROLEUM (letter/digit mix), 63c (letter/digit mix), 131c (letter/digit mix) :: 13PRTROLEUMâ€”Crude, at 63c. ; refined, 131c. to</t>
-        </is>
-      </c>
-      <c r="L190" s="1" t="inlineStr"/>
-      <c r="M190" s="1" t="inlineStr"/>
-      <c r="N190" s="1" t="inlineStr"/>
-      <c r="O190" s="1" t="inlineStr"/>
-      <c r="P190" s="1" t="inlineStr"/>
-      <c r="Q190" s="1" t="inlineStr"/>
-      <c r="R190" s="1" t="inlineStr"/>
-      <c r="S190" s="1" t="inlineStr"/>
-      <c r="T190" s="1" t="inlineStr"/>
-      <c r="U190" s="1" t="inlineStr"/>
-      <c r="V190" s="1" t="inlineStr"/>
-      <c r="W190" s="1" t="inlineStr"/>
-      <c r="X190" s="1" t="inlineStr"/>
-      <c r="Y190" s="1" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="inlineStr"/>
-      <c r="B191" s="1" t="inlineStr"/>
-      <c r="C191" s="1" t="inlineStr"/>
-      <c r="D191" s="1" t="inlineStr"/>
-      <c r="E191" s="1" t="inlineStr"/>
-      <c r="F191" s="1" t="inlineStr"/>
-      <c r="G191" s="1" t="inlineStr"/>
-      <c r="H191" s="1" t="inlineStr"/>
-      <c r="I191" s="1" t="inlineStr"/>
-      <c r="J191" s="1" t="inlineStr"/>
-      <c r="K191" s="1" t="inlineStr">
-        <is>
-          <t>L2667: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BREADSTUFFSâ€”Quiet.</t>
-        </is>
-      </c>
-      <c r="L191" s="1" t="inlineStr"/>
-      <c r="M191" s="1" t="inlineStr"/>
-      <c r="N191" s="1" t="inlineStr"/>
-      <c r="O191" s="1" t="inlineStr"/>
-      <c r="P191" s="1" t="inlineStr"/>
-      <c r="Q191" s="1" t="inlineStr"/>
-      <c r="R191" s="1" t="inlineStr"/>
-      <c r="S191" s="1" t="inlineStr"/>
-      <c r="T191" s="1" t="inlineStr"/>
-      <c r="U191" s="1" t="inlineStr"/>
-      <c r="V191" s="1" t="inlineStr"/>
-      <c r="W191" s="1" t="inlineStr"/>
-      <c r="X191" s="1" t="inlineStr"/>
-      <c r="Y191" s="1" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr"/>
-      <c r="B192" s="1" t="inlineStr"/>
-      <c r="C192" s="1" t="inlineStr"/>
-      <c r="D192" s="1" t="inlineStr"/>
-      <c r="E192" s="1" t="inlineStr"/>
-      <c r="F192" s="1" t="inlineStr"/>
-      <c r="G192" s="1" t="inlineStr"/>
-      <c r="H192" s="1" t="inlineStr"/>
-      <c r="I192" s="1" t="inlineStr"/>
-      <c r="J192" s="1" t="inlineStr"/>
-      <c r="K192" s="1" t="inlineStr">
-        <is>
-          <t>L2669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WHEATâ€”At 9s to 9s 4d per cental for club Cali-</t>
-        </is>
-      </c>
-      <c r="L192" s="1" t="inlineStr"/>
-      <c r="M192" s="1" t="inlineStr"/>
-      <c r="N192" s="1" t="inlineStr"/>
-      <c r="O192" s="1" t="inlineStr"/>
-      <c r="P192" s="1" t="inlineStr"/>
-      <c r="Q192" s="1" t="inlineStr"/>
-      <c r="R192" s="1" t="inlineStr"/>
-      <c r="S192" s="1" t="inlineStr"/>
-      <c r="T192" s="1" t="inlineStr"/>
-      <c r="U192" s="1" t="inlineStr"/>
-      <c r="V192" s="1" t="inlineStr"/>
-      <c r="W192" s="1" t="inlineStr"/>
-      <c r="X192" s="1" t="inlineStr"/>
-      <c r="Y192" s="1" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="1" t="inlineStr"/>
-      <c r="B193" s="1" t="inlineStr"/>
-      <c r="C193" s="1" t="inlineStr"/>
-      <c r="D193" s="1" t="inlineStr"/>
-      <c r="E193" s="1" t="inlineStr"/>
-      <c r="F193" s="1" t="inlineStr"/>
-      <c r="G193" s="1" t="inlineStr"/>
-      <c r="H193" s="1" t="inlineStr"/>
-      <c r="I193" s="1" t="inlineStr"/>
-      <c r="J193" s="1" t="inlineStr"/>
-      <c r="K193" s="1" t="inlineStr">
-        <is>
-          <t>L2672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CORNâ€”At 31s to 31s 3d per quarter.</t>
-        </is>
-      </c>
-      <c r="L193" s="1" t="inlineStr"/>
-      <c r="M193" s="1" t="inlineStr"/>
-      <c r="N193" s="1" t="inlineStr"/>
-      <c r="O193" s="1" t="inlineStr"/>
-      <c r="P193" s="1" t="inlineStr"/>
-      <c r="Q193" s="1" t="inlineStr"/>
-      <c r="R193" s="1" t="inlineStr"/>
-      <c r="S193" s="1" t="inlineStr"/>
-      <c r="T193" s="1" t="inlineStr"/>
-      <c r="U193" s="1" t="inlineStr"/>
-      <c r="V193" s="1" t="inlineStr"/>
-      <c r="W193" s="1" t="inlineStr"/>
-      <c r="X193" s="1" t="inlineStr"/>
-      <c r="Y193" s="1" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="1" t="inlineStr"/>
-      <c r="B194" s="1" t="inlineStr"/>
-      <c r="C194" s="1" t="inlineStr"/>
-      <c r="D194" s="1" t="inlineStr"/>
-      <c r="E194" s="1" t="inlineStr"/>
-      <c r="F194" s="1" t="inlineStr"/>
-      <c r="G194" s="1" t="inlineStr"/>
-      <c r="H194" s="1" t="inlineStr"/>
-      <c r="I194" s="1" t="inlineStr"/>
-      <c r="J194" s="1" t="inlineStr"/>
-      <c r="K194" s="1" t="inlineStr">
-        <is>
-          <t>L2674: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PEASâ€”At 39s per quarter for Canadjan,</t>
-        </is>
-      </c>
-      <c r="L194" s="1" t="inlineStr"/>
-      <c r="M194" s="1" t="inlineStr"/>
-      <c r="N194" s="1" t="inlineStr"/>
-      <c r="O194" s="1" t="inlineStr"/>
-      <c r="P194" s="1" t="inlineStr"/>
-      <c r="Q194" s="1" t="inlineStr"/>
-      <c r="R194" s="1" t="inlineStr"/>
-      <c r="S194" s="1" t="inlineStr"/>
-      <c r="T194" s="1" t="inlineStr"/>
-      <c r="U194" s="1" t="inlineStr"/>
-      <c r="V194" s="1" t="inlineStr"/>
-      <c r="W194" s="1" t="inlineStr"/>
-      <c r="X194" s="1" t="inlineStr"/>
-      <c r="Y194" s="1" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="inlineStr"/>
-      <c r="B195" s="1" t="inlineStr"/>
-      <c r="C195" s="1" t="inlineStr"/>
-      <c r="D195" s="1" t="inlineStr"/>
-      <c r="E195" s="1" t="inlineStr"/>
-      <c r="F195" s="1" t="inlineStr"/>
-      <c r="G195" s="1" t="inlineStr"/>
-      <c r="H195" s="1" t="inlineStr"/>
-      <c r="I195" s="1" t="inlineStr"/>
-      <c r="J195" s="1" t="inlineStr"/>
-      <c r="K195" s="1" t="inlineStr">
-        <is>
-          <t>L2675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TALLOWâ€”40S 6d per cwt,</t>
-        </is>
-      </c>
-      <c r="L195" s="1" t="inlineStr"/>
-      <c r="M195" s="1" t="inlineStr"/>
-      <c r="N195" s="1" t="inlineStr"/>
-      <c r="O195" s="1" t="inlineStr"/>
-      <c r="P195" s="1" t="inlineStr"/>
-      <c r="Q195" s="1" t="inlineStr"/>
-      <c r="R195" s="1" t="inlineStr"/>
-      <c r="S195" s="1" t="inlineStr"/>
-      <c r="T195" s="1" t="inlineStr"/>
-      <c r="U195" s="1" t="inlineStr"/>
-      <c r="V195" s="1" t="inlineStr"/>
-      <c r="W195" s="1" t="inlineStr"/>
-      <c r="X195" s="1" t="inlineStr"/>
-      <c r="Y195" s="1" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="inlineStr"/>
-      <c r="B196" s="1" t="inlineStr"/>
-      <c r="C196" s="1" t="inlineStr"/>
-      <c r="D196" s="1" t="inlineStr"/>
-      <c r="E196" s="1" t="inlineStr"/>
-      <c r="F196" s="1" t="inlineStr"/>
-      <c r="G196" s="1" t="inlineStr"/>
-      <c r="H196" s="1" t="inlineStr"/>
-      <c r="I196" s="1" t="inlineStr"/>
-      <c r="J196" s="1" t="inlineStr"/>
-      <c r="K196" s="1" t="inlineStr">
-        <is>
-          <t>L2677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 'JEWELLERY AT COST.â€”Attention is directed</t>
-        </is>
-      </c>
-      <c r="L196" s="1" t="inlineStr"/>
-      <c r="M196" s="1" t="inlineStr"/>
-      <c r="N196" s="1" t="inlineStr"/>
-      <c r="O196" s="1" t="inlineStr"/>
-      <c r="P196" s="1" t="inlineStr"/>
-      <c r="Q196" s="1" t="inlineStr"/>
-      <c r="R196" s="1" t="inlineStr"/>
-      <c r="S196" s="1" t="inlineStr"/>
-      <c r="T196" s="1" t="inlineStr"/>
-      <c r="U196" s="1" t="inlineStr"/>
-      <c r="V196" s="1" t="inlineStr"/>
-      <c r="W196" s="1" t="inlineStr"/>
-      <c r="X196" s="1" t="inlineStr"/>
-      <c r="Y196" s="1" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr"/>
-      <c r="B197" s="1" t="inlineStr"/>
-      <c r="C197" s="1" t="inlineStr"/>
-      <c r="D197" s="1" t="inlineStr"/>
-      <c r="E197" s="1" t="inlineStr"/>
-      <c r="F197" s="1" t="inlineStr"/>
-      <c r="G197" s="1" t="inlineStr"/>
-      <c r="H197" s="1" t="inlineStr"/>
-      <c r="I197" s="1" t="inlineStr"/>
-      <c r="J197" s="1" t="inlineStr"/>
-      <c r="K197" s="1" t="inlineStr">
-        <is>
-          <t>L2678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to Mr. Campbellâ€™s advertisement in another</t>
-        </is>
-      </c>
-      <c r="L197" s="1" t="inlineStr"/>
-      <c r="M197" s="1" t="inlineStr"/>
-      <c r="N197" s="1" t="inlineStr"/>
-      <c r="O197" s="1" t="inlineStr"/>
-      <c r="P197" s="1" t="inlineStr"/>
-      <c r="Q197" s="1" t="inlineStr"/>
-      <c r="R197" s="1" t="inlineStr"/>
-      <c r="S197" s="1" t="inlineStr"/>
-      <c r="T197" s="1" t="inlineStr"/>
-      <c r="U197" s="1" t="inlineStr"/>
-      <c r="V197" s="1" t="inlineStr"/>
-      <c r="W197" s="1" t="inlineStr"/>
-      <c r="X197" s="1" t="inlineStr"/>
-      <c r="Y197" s="1" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr"/>
-      <c r="B198" s="1" t="inlineStr"/>
-      <c r="C198" s="1" t="inlineStr"/>
-      <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr"/>
-      <c r="F198" s="1" t="inlineStr"/>
-      <c r="G198" s="1" t="inlineStr"/>
-      <c r="H198" s="1" t="inlineStr"/>
-      <c r="I198" s="1" t="inlineStr"/>
-      <c r="J198" s="1" t="inlineStr"/>
-      <c r="K198" s="1" t="inlineStr">
-        <is>
-          <t>L2691: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FIRE.â€”A rather curious circumstance hap-</t>
-        </is>
-      </c>
-      <c r="L198" s="1" t="inlineStr"/>
-      <c r="M198" s="1" t="inlineStr"/>
-      <c r="N198" s="1" t="inlineStr"/>
-      <c r="O198" s="1" t="inlineStr"/>
-      <c r="P198" s="1" t="inlineStr"/>
-      <c r="Q198" s="1" t="inlineStr"/>
-      <c r="R198" s="1" t="inlineStr"/>
-      <c r="S198" s="1" t="inlineStr"/>
-      <c r="T198" s="1" t="inlineStr"/>
-      <c r="U198" s="1" t="inlineStr"/>
-      <c r="V198" s="1" t="inlineStr"/>
-      <c r="W198" s="1" t="inlineStr"/>
-      <c r="X198" s="1" t="inlineStr"/>
-      <c r="Y198" s="1" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr"/>
-      <c r="B199" s="1" t="inlineStr"/>
-      <c r="C199" s="1" t="inlineStr"/>
-      <c r="D199" s="1" t="inlineStr"/>
-      <c r="E199" s="1" t="inlineStr"/>
-      <c r="F199" s="1" t="inlineStr"/>
-      <c r="G199" s="1" t="inlineStr"/>
-      <c r="H199" s="1" t="inlineStr"/>
-      <c r="I199" s="1" t="inlineStr"/>
-      <c r="J199" s="1" t="inlineStr"/>
-      <c r="K199" s="1" t="inlineStr">
-        <is>
-          <t>L2710: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NIAGARA, June 8th.â€”Major-General Smyth</t>
-        </is>
-      </c>
-      <c r="L199" s="1" t="inlineStr"/>
-      <c r="M199" s="1" t="inlineStr"/>
-      <c r="N199" s="1" t="inlineStr"/>
-      <c r="O199" s="1" t="inlineStr"/>
-      <c r="P199" s="1" t="inlineStr"/>
-      <c r="Q199" s="1" t="inlineStr"/>
-      <c r="R199" s="1" t="inlineStr"/>
-      <c r="S199" s="1" t="inlineStr"/>
-      <c r="T199" s="1" t="inlineStr"/>
-      <c r="U199" s="1" t="inlineStr"/>
-      <c r="V199" s="1" t="inlineStr"/>
-      <c r="W199" s="1" t="inlineStr"/>
-      <c r="X199" s="1" t="inlineStr"/>
-      <c r="Y199" s="1" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="inlineStr"/>
-      <c r="B200" s="1" t="inlineStr"/>
-      <c r="C200" s="1" t="inlineStr"/>
-      <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr"/>
-      <c r="F200" s="1" t="inlineStr"/>
-      <c r="G200" s="1" t="inlineStr"/>
-      <c r="H200" s="1" t="inlineStr"/>
-      <c r="I200" s="1" t="inlineStr"/>
-      <c r="J200" s="1" t="inlineStr"/>
-      <c r="K200" s="1" t="inlineStr">
-        <is>
-          <t>L2712: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ronto by this eveningâ€™s boat.</t>
-        </is>
-      </c>
-      <c r="L200" s="1" t="inlineStr"/>
-      <c r="M200" s="1" t="inlineStr"/>
-      <c r="N200" s="1" t="inlineStr"/>
-      <c r="O200" s="1" t="inlineStr"/>
-      <c r="P200" s="1" t="inlineStr"/>
-      <c r="Q200" s="1" t="inlineStr"/>
-      <c r="R200" s="1" t="inlineStr"/>
-      <c r="S200" s="1" t="inlineStr"/>
-      <c r="T200" s="1" t="inlineStr"/>
-      <c r="U200" s="1" t="inlineStr"/>
-      <c r="V200" s="1" t="inlineStr"/>
-      <c r="W200" s="1" t="inlineStr"/>
-      <c r="X200" s="1" t="inlineStr"/>
-      <c r="Y200" s="1" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="inlineStr"/>
-      <c r="B201" s="1" t="inlineStr"/>
-      <c r="C201" s="1" t="inlineStr"/>
-      <c r="D201" s="1" t="inlineStr"/>
-      <c r="E201" s="1" t="inlineStr"/>
-      <c r="F201" s="1" t="inlineStr"/>
-      <c r="G201" s="1" t="inlineStr"/>
-      <c r="H201" s="1" t="inlineStr"/>
-      <c r="I201" s="1" t="inlineStr"/>
-      <c r="J201" s="1" t="inlineStr"/>
-      <c r="K201" s="1" t="inlineStr">
-        <is>
-          <t>L2735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L201" s="1" t="inlineStr"/>
-      <c r="M201" s="1" t="inlineStr"/>
-      <c r="N201" s="1" t="inlineStr"/>
-      <c r="O201" s="1" t="inlineStr"/>
-      <c r="P201" s="1" t="inlineStr"/>
-      <c r="Q201" s="1" t="inlineStr"/>
-      <c r="R201" s="1" t="inlineStr"/>
-      <c r="S201" s="1" t="inlineStr"/>
-      <c r="T201" s="1" t="inlineStr"/>
-      <c r="U201" s="1" t="inlineStr"/>
-      <c r="V201" s="1" t="inlineStr"/>
-      <c r="W201" s="1" t="inlineStr"/>
-      <c r="X201" s="1" t="inlineStr"/>
-      <c r="Y201" s="1" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="inlineStr"/>
-      <c r="B202" s="1" t="inlineStr"/>
-      <c r="C202" s="1" t="inlineStr"/>
-      <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr"/>
-      <c r="F202" s="1" t="inlineStr"/>
-      <c r="G202" s="1" t="inlineStr"/>
-      <c r="H202" s="1" t="inlineStr"/>
-      <c r="I202" s="1" t="inlineStr"/>
-      <c r="J202" s="1" t="inlineStr"/>
-      <c r="K202" s="1" t="inlineStr">
-        <is>
-          <t>L2747: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Send for Circularâ€™and Specimen of Penmanship</t>
-        </is>
-      </c>
-      <c r="L202" s="1" t="inlineStr"/>
-      <c r="M202" s="1" t="inlineStr"/>
-      <c r="N202" s="1" t="inlineStr"/>
-      <c r="O202" s="1" t="inlineStr"/>
-      <c r="P202" s="1" t="inlineStr"/>
-      <c r="Q202" s="1" t="inlineStr"/>
-      <c r="R202" s="1" t="inlineStr"/>
-      <c r="S202" s="1" t="inlineStr"/>
-      <c r="T202" s="1" t="inlineStr"/>
-      <c r="U202" s="1" t="inlineStr"/>
-      <c r="V202" s="1" t="inlineStr"/>
-      <c r="W202" s="1" t="inlineStr"/>
-      <c r="X202" s="1" t="inlineStr"/>
-      <c r="Y202" s="1" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="1" t="inlineStr"/>
-      <c r="B203" s="1" t="inlineStr"/>
-      <c r="C203" s="1" t="inlineStr"/>
-      <c r="D203" s="1" t="inlineStr"/>
-      <c r="E203" s="1" t="inlineStr"/>
-      <c r="F203" s="1" t="inlineStr"/>
-      <c r="G203" s="1" t="inlineStr"/>
-      <c r="H203" s="1" t="inlineStr"/>
-      <c r="I203" s="1" t="inlineStr"/>
-      <c r="J203" s="1" t="inlineStr"/>
-      <c r="K203" s="1" t="inlineStr">
-        <is>
-          <t>L2763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L203" s="1" t="inlineStr"/>
-      <c r="M203" s="1" t="inlineStr"/>
-      <c r="N203" s="1" t="inlineStr"/>
-      <c r="O203" s="1" t="inlineStr"/>
-      <c r="P203" s="1" t="inlineStr"/>
-      <c r="Q203" s="1" t="inlineStr"/>
-      <c r="R203" s="1" t="inlineStr"/>
-      <c r="S203" s="1" t="inlineStr"/>
-      <c r="T203" s="1" t="inlineStr"/>
-      <c r="U203" s="1" t="inlineStr"/>
-      <c r="V203" s="1" t="inlineStr"/>
-      <c r="W203" s="1" t="inlineStr"/>
-      <c r="X203" s="1" t="inlineStr"/>
-      <c r="Y203" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
